--- a/AAII_Financials/Quarterly/SOL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
   <si>
     <t>SOL</t>
   </si>
@@ -656,429 +656,442 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42551</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E8" s="3">
         <v>33800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>28900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>22800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>15500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>18500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>22800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>26200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>21200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>26500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>66000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>13600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>13100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>18800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>27800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>44800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>103000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>36300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>151600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>156600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>232100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>187000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>250000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>260700</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E9" s="3">
         <v>21200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>20300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>18800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>19800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>49700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>12700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>10200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>19600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>36400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>88800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>29900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>147500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>154900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>227100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>168200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>208900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>216200</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E10" s="3">
         <v>12600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>7400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>7100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>16300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>10500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>8600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>8400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>14200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>6400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>5000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>18800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>41100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>44500</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,8 +1125,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1189,26 +1203,29 @@
       <c r="AA12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AB12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC12" s="3">
         <v>5400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>5700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>5400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>6300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>7400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1319,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1313,59 +1333,59 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>400</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>300</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>1000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>5500</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
@@ -1373,8 +1393,8 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1382,23 +1402,26 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3">
         <v>4700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-100</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,8 +1515,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1550,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E17" s="3">
         <v>28800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>23800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>24300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>21600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>22300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>39800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>58600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>21900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>38900</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AB17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC17" s="3">
         <v>172000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>174400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>254000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>198800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>243700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>248200</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E18" s="3">
         <v>5000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-13300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>5700</v>
-      </c>
-      <c r="X18" s="3">
-        <v>5900</v>
       </c>
       <c r="Y18" s="3">
         <v>5900</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>8</v>
+      <c r="Z18" s="3">
+        <v>5900</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-20400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-17800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-21900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-11800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>6300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,139 +1782,143 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2600</v>
+        <v>-4800</v>
       </c>
       <c r="E20" s="3">
         <v>2600</v>
       </c>
       <c r="F20" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G20" s="3">
         <v>900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1100</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>7200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>8100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E21" s="3">
         <v>7100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>500</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="3">
         <v>-700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4400</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1921,26 +1958,29 @@
       <c r="AA21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>9400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>5700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>32500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>37200</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1950,250 +1990,256 @@
       <c r="E22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1700</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1000</v>
       </c>
       <c r="L22" s="3">
         <v>1000</v>
       </c>
       <c r="M22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N22" s="3">
         <v>1500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>3900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>8600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>9200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>7400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>8200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>8500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E23" s="3">
         <v>7600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-14300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-29100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-26900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-22100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-22400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>400</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>-200</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
@@ -2201,31 +2247,34 @@
         <v>0</v>
       </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>300</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB24" s="3">
+      <c r="AB24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC24" s="3">
         <v>2400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-1900</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>400</v>
       </c>
       <c r="AG24" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2368,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E26" s="3">
         <v>7700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3500</v>
       </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
       <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
         <v>-2000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-14500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>6500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>5400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3200</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB26" s="3">
+      <c r="AB26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-31500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-23200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-25500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-20500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>5500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E27" s="3">
         <v>8300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-10900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3200</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB27" s="3">
+      <c r="AB27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-31500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-23200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-25500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-20500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>5500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2662,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2657,17 +2718,17 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2675,8 +2736,8 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
@@ -2699,8 +2760,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,198 +2956,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2600</v>
+        <v>4800</v>
       </c>
       <c r="E32" s="3">
         <v>-2600</v>
       </c>
       <c r="F32" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="G32" s="3">
         <v>-900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC32" s="3">
         <v>100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-7200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-8100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E33" s="3">
         <v>8300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-10900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3200</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB33" s="3">
+      <c r="AB33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-31500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-23200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-25500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-20500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>5500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3250,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E35" s="3">
         <v>8300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-10900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3200</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB35" s="3">
+      <c r="AB35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-31500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-23200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-25500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-20500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>5500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42551</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,103 +3525,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>59200</v>
+      </c>
+      <c r="E41" s="3">
         <v>60500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>66700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>107100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>123000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>207900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>222900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>254100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>275400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>286000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>301000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>40600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>15600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>15500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>24300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>24800</v>
       </c>
-      <c r="Y41" s="3">
-        <v>0</v>
-      </c>
       <c r="Z41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3">
         <v>13400</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB41" s="3">
+      <c r="AB41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC41" s="3">
         <v>28600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>26600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>37300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>28800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>23700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3543,11 +3633,11 @@
         <v>10100</v>
       </c>
       <c r="E42" s="3">
+        <v>10100</v>
+      </c>
+      <c r="F42" s="3">
         <v>10000</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3560,8 +3650,8 @@
       <c r="J42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
+      <c r="K42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -3629,103 +3719,109 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>76500</v>
+      </c>
+      <c r="E43" s="3">
         <v>86400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>79100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>71500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>52700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>39400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>46700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>50400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>48300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>39600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>36000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>23800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>24700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>29500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>21000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>21300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>46600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>49300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>50700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>47300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>55900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>58900</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
-      </c>
       <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3">
         <v>38500</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB43" s="3">
+      <c r="AB43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC43" s="3">
         <v>134000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>129700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>134100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>204000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>195900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>199000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3783,17 +3879,17 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W44" s="3">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X44" s="3">
         <v>200</v>
       </c>
-      <c r="X44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="3" t="s">
-        <v>8</v>
+      <c r="Y44" s="3">
+        <v>0</v>
       </c>
       <c r="Z44" s="3" t="s">
         <v>8</v>
@@ -3801,227 +3897,236 @@
       <c r="AA44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AB44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC44" s="3">
         <v>92300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>153200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>144000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>185200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>165500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>181700</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>67800</v>
+      </c>
+      <c r="E45" s="3">
         <v>72200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>54900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>42100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>36000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>38400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>38800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>24700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>27500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>31500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>33200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>72300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>32300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>27600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>47700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>57400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>50800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>80900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>80500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>81200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>73800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>91600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>118100</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB45" s="3">
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC45" s="3">
         <v>264300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>233600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>192100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>194500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>248100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>232700</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>213500</v>
+      </c>
+      <c r="E46" s="3">
         <v>229100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>210700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>220700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>211700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>285700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>308400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>329200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>351200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>357100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>370200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>136700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>72500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>68400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>84200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>103100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>106800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>138900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>138200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>135300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>138000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>175300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>170100</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB46" s="3">
+      <c r="AB46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC46" s="3">
         <v>519200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>543200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>507500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>612500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>633100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>652100</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" s="3">
-        <v>10000</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G47" s="3">
         <v>10000</v>
@@ -4032,8 +4137,8 @@
       <c r="I47" s="3">
         <v>10000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
+      <c r="J47" s="3">
+        <v>10000</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
@@ -4050,8 +4155,8 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4104,108 +4209,114 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>189100</v>
+      </c>
+      <c r="E48" s="3">
         <v>192800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>216500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>214800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>202700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>160600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>166300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>167100</v>
-      </c>
-      <c r="K48" s="3">
-        <v>167300</v>
       </c>
       <c r="L48" s="3">
         <v>167300</v>
       </c>
       <c r="M48" s="3">
+        <v>167300</v>
+      </c>
+      <c r="N48" s="3">
         <v>166200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>168700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>186900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>183200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>187500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>192300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>211400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>249000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>226100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>190800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>192500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>195900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>154700</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC48" s="3">
         <v>537600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>486300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>491300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>547700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>568100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>603200</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
         <v>1000</v>
@@ -4237,8 +4348,8 @@
       <c r="N49" s="3">
         <v>1000</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>8</v>
+      <c r="O49" s="3">
+        <v>1000</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>8</v>
@@ -4255,8 +4366,8 @@
       <c r="T49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -4270,32 +4381,35 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>8</v>
+      <c r="Z49" s="3">
+        <v>0</v>
       </c>
       <c r="AA49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AB49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC49" s="3">
         <v>32200</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>31900</v>
       </c>
       <c r="AD49" s="3">
         <v>31900</v>
       </c>
       <c r="AE49" s="3">
+        <v>31900</v>
+      </c>
+      <c r="AF49" s="3">
         <v>35500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>35800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>37200</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,103 +4601,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>51800</v>
+      </c>
+      <c r="E52" s="3">
         <v>54700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>53500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>47200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>41800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>42900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>34200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>31900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>36400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>33800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>29700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>30400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>29700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>26500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>25300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>24600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>14500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>18400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>53400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>51700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>44900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>18500</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
-      </c>
       <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3">
         <v>11000</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB52" s="3">
+      <c r="AB52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC52" s="3">
         <v>66000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>65000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>57800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>50800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>51700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>46400</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4797,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>454400</v>
+      </c>
+      <c r="E54" s="3">
         <v>477700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>481700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>493900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>467200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>500300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>519900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>529300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>556000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>559200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>567100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>336900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>289100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>278000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>296900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>319900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>332700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>406300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>417700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>377700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>375400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>389600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>335700</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB54" s="3">
+      <c r="AB54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC54" s="3">
         <v>1154900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1126300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1088400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1246600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1288700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1338900</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,578 +4969,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E57" s="3">
         <v>5400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>20400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>12500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>12100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>24600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>23700</v>
       </c>
-      <c r="Y57" s="3">
-        <v>0</v>
-      </c>
       <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="3">
         <v>25800</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB57" s="3">
+      <c r="AB57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC57" s="3">
         <v>203200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>221600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>223300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>281300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>280600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>302000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E58" s="3">
         <v>6700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>12200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>23000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>49100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>43500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>42100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>43900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>47800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>57100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>108900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>101900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>44500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>7100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>15100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>23700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>6600</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB58" s="3">
+      <c r="AB58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC58" s="3">
         <v>671400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>647600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>595400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>699000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>716500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>735600</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E59" s="3">
         <v>29800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>27900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>25200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>17400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>17700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>20000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>19300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>19600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>23500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>32900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>19900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>27000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>38600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>41100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>42400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>43100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>56500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>77200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>61600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>73500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>112800</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB59" s="3">
+      <c r="AB59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC59" s="3">
         <v>150800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>101600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>85700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>82600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>89900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>91500</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E60" s="3">
         <v>41800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>43700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>43300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>34000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>31100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>33800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>35100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>36400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>36500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>51100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>88300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>73200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>75900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>89400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>109400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>113500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>162800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>170900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>133700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>93300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>104700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>145200</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB60" s="3">
+      <c r="AB60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC60" s="3">
         <v>1025400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>970800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>904400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1062900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1087000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1129100</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>33300</v>
+      </c>
+      <c r="E61" s="3">
         <v>35400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>37400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>37500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>38000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>21200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>26900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>30000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>31700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>36100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>38800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>44000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>48100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>44800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>52500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>50100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>68400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>81200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>89100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>119300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>153200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>157800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>32500</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>30300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>31100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>28800</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
       <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E62" s="3">
         <v>21600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>24100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>24400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>15500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>15400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>15500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>19500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>19700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>20100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>21400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>20400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>21200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>22600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>22900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>21500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>33600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>35300</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
+      <c r="X62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y62" s="3">
         <v>0</v>
       </c>
       <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3">
         <v>67500</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB62" s="3">
+      <c r="AB62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC62" s="3">
         <v>84400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>82600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>89000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>92000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>89500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>93600</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +5849,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>132100</v>
+      </c>
+      <c r="E66" s="3">
         <v>137200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>146000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>146600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>128100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>110100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>120400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>125300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>133000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>137200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>153800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>197800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>185700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>184400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>206600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>225200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>238300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>313900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>329600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>287000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>280700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>294400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>245200</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB66" s="3">
+      <c r="AB66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC66" s="3">
         <v>1141000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1084400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1022300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1154900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1176400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1224200</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6375,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-438600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-429200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-437600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-437400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-431600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-434600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-434400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-432700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-431100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-431800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-438800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-439600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-441500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-443700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-446700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-442300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-431400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-433800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-438900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-433500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-428400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-429900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-435500</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC72" s="3">
         <v>-524700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-493200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-470000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-444500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-424000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-429500</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6767,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>322300</v>
+      </c>
+      <c r="E76" s="3">
         <v>340500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>335700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>347300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>339100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>390200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>399500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>404000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>422900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>422000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>413300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>139100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>103300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>93600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>90300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>94700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>94400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>92400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>88100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>90700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>94800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>95200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>90500</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB76" s="3">
+      <c r="AB76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC76" s="3">
         <v>13900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>41900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>66100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>91700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>112300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>114700</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6963,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42551</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E81" s="3">
         <v>8300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-10900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3200</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB81" s="3">
+      <c r="AB81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-31500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-23200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-25500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-20500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>5500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,8 +7202,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7072,35 +7271,38 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z83" s="3">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA83" s="3">
         <v>4500</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB83" s="3">
+      <c r="AB83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC83" s="3">
         <v>17800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>20900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>24100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>19900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>18100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,56 +7788,59 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-23700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-10600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-14400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>8800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-10500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-9900</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>8</v>
       </c>
@@ -7639,38 +7856,41 @@
       <c r="W89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="X89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA89" s="3">
         <v>18400</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB89" s="3">
+      <c r="AB89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-33800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>44600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-9100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,8 +7924,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7772,35 +7993,38 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-80300</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AB91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-11300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-11400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,56 +8216,59 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E94" s="3">
         <v>100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-31200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>26100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1200</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>8</v>
       </c>
@@ -8054,38 +8284,41 @@
       <c r="W94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-156400</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="AB94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-30100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>17900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>26000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>5200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8352,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8214,8 +8448,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,56 +8742,59 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E100" s="3">
         <v>1200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-16200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-45700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-14200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-23700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-14300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>244800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>32600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>8300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1400</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>8</v>
       </c>
@@ -8564,86 +8810,89 @@
       <c r="W100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA100" s="3">
         <v>102400</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AB100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC100" s="3">
         <v>16000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>50700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-48900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-4200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1900</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>8</v>
       </c>
@@ -8659,86 +8908,89 @@
       <c r="W101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="X101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA101" s="3">
         <v>11600</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB101" s="3">
+      <c r="AB101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>2500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-6800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-40600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-15700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-85000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-14900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-31500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-21500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>260300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>24300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8100</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>8</v>
       </c>
@@ -8754,34 +9006,37 @@
       <c r="W102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="X102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-23900</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AB102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC102" s="3">
         <v>2000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-10700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>8500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>5100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-15000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
   <si>
     <t>SOL</t>
   </si>
@@ -656,442 +656,480 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AJ7" s="2">
         <v>42551</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AK7" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>14600</v>
+      </c>
+      <c r="F8" s="3">
+        <v>45000</v>
+      </c>
+      <c r="G8" s="3">
         <v>13900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="H8" s="3">
         <v>33800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="I8" s="3">
         <v>12900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="J8" s="3">
         <v>20700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="K8" s="3">
         <v>28900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="L8" s="3">
         <v>8200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="M8" s="3">
         <v>3500</v>
-      </c>
-      <c r="K8" s="3">
-        <v>22800</v>
-      </c>
-      <c r="L8" s="3">
-        <v>15500</v>
-      </c>
-      <c r="M8" s="3">
-        <v>18500</v>
       </c>
       <c r="N8" s="3">
         <v>22800</v>
       </c>
       <c r="O8" s="3">
+        <v>15500</v>
+      </c>
+      <c r="P8" s="3">
+        <v>18500</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>22800</v>
+      </c>
+      <c r="R8" s="3">
         <v>16400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="S8" s="3">
         <v>9700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="T8" s="3">
         <v>26200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="U8" s="3">
         <v>21200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="V8" s="3">
         <v>26500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="W8" s="3">
         <v>66000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="X8" s="3">
         <v>13600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Y8" s="3">
         <v>13100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Z8" s="3">
         <v>5600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="AA8" s="3">
         <v>18800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AB8" s="3">
         <v>27800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AC8" s="3">
         <v>44800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AD8" s="3">
         <v>103000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AE8" s="3">
         <v>36300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AF8" s="3">
         <v>151600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AG8" s="3">
         <v>156600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AH8" s="3">
         <v>232100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AI8" s="3">
         <v>187000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AJ8" s="3">
         <v>250000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AK8" s="3">
         <v>260700</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>10300</v>
+      </c>
+      <c r="F9" s="3">
+        <v>39900</v>
+      </c>
+      <c r="G9" s="3">
         <v>8300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="H9" s="3">
         <v>21200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="I9" s="3">
         <v>11300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="J9" s="3">
         <v>18700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="K9" s="3">
         <v>20300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="L9" s="3">
         <v>4500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="M9" s="3">
         <v>2400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="N9" s="3">
         <v>15600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="O9" s="3">
         <v>9500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="P9" s="3">
         <v>7200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="Q9" s="3">
         <v>16000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="R9" s="3">
         <v>14400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="S9" s="3">
         <v>3800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="T9" s="3">
         <v>18800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="U9" s="3">
         <v>19800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="V9" s="3">
         <v>19400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="W9" s="3">
         <v>49700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="X9" s="3">
         <v>3100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="Y9" s="3">
         <v>12700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Z9" s="3">
         <v>2700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="AA9" s="3">
         <v>10200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AB9" s="3">
         <v>19600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AC9" s="3">
         <v>36400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AD9" s="3">
         <v>88800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AE9" s="3">
         <v>29900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AF9" s="3">
         <v>147500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AG9" s="3">
         <v>154900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AH9" s="3">
         <v>227100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AI9" s="3">
         <v>168200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AJ9" s="3">
         <v>208900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AK9" s="3">
         <v>216200</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F10" s="3">
+        <v>5100</v>
+      </c>
+      <c r="G10" s="3">
         <v>5600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="H10" s="3">
         <v>12600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="I10" s="3">
         <v>1600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="J10" s="3">
         <v>2000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="K10" s="3">
         <v>8600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="L10" s="3">
         <v>3700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="M10" s="3">
         <v>1100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="N10" s="3">
         <v>7200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="O10" s="3">
         <v>6000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="P10" s="3">
         <v>11300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="Q10" s="3">
         <v>6800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="R10" s="3">
         <v>2000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="S10" s="3">
         <v>5900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="T10" s="3">
         <v>7400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="U10" s="3">
         <v>1400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="V10" s="3">
         <v>7100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="W10" s="3">
         <v>16300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="X10" s="3">
         <v>10500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Y10" s="3">
         <v>400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Z10" s="3">
         <v>2900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="AA10" s="3">
         <v>8600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AB10" s="3">
         <v>8200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AC10" s="3">
         <v>8400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AD10" s="3">
         <v>14200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AE10" s="3">
         <v>6400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AF10" s="3">
         <v>4100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AG10" s="3">
         <v>1700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AH10" s="3">
         <v>5000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AI10" s="3">
         <v>18800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AJ10" s="3">
         <v>41100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AK10" s="3">
         <v>44500</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1126,8 +1164,11 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,26 +1247,35 @@
       <c r="AB12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF12" s="3">
         <v>5400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AG12" s="3">
         <v>5700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AH12" s="3">
         <v>5400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AI12" s="3">
         <v>6300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AJ12" s="3">
         <v>7400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AK12" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,8 +1372,17 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1333,11 +1392,11 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="F14" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1348,80 +1407,89 @@
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>400</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>300</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>1000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="U14" s="3">
         <v>100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="V14" s="3">
         <v>1300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="W14" s="3">
         <v>5500</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
         <v>4700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AI14" s="3">
         <v>-100</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3">
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1518,8 +1586,17 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1551,204 +1628,225 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>15800</v>
+      </c>
+      <c r="F17" s="3">
+        <v>51700</v>
+      </c>
+      <c r="G17" s="3">
         <v>17900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="H17" s="3">
         <v>28800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="I17" s="3">
         <v>15900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="J17" s="3">
         <v>25900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="K17" s="3">
         <v>23800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="L17" s="3">
         <v>8400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="M17" s="3">
         <v>5700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="N17" s="3">
         <v>24300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="O17" s="3">
         <v>12800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="P17" s="3">
         <v>11200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="Q17" s="3">
         <v>18700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="R17" s="3">
         <v>15900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="S17" s="3">
         <v>6900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="T17" s="3">
         <v>21600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="U17" s="3">
         <v>22300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="V17" s="3">
         <v>39800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="W17" s="3">
         <v>58600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="X17" s="3">
         <v>6500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Y17" s="3">
         <v>15200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Z17" s="3">
         <v>7500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="AA17" s="3">
         <v>13100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AB17" s="3">
         <v>21900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AC17" s="3">
         <v>38900</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF17" s="3">
         <v>172000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AG17" s="3">
         <v>174400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AH17" s="3">
         <v>254000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AI17" s="3">
         <v>198800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AJ17" s="3">
         <v>243700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AK17" s="3">
         <v>248200</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="G18" s="3">
         <v>-4000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="H18" s="3">
         <v>5000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="I18" s="3">
         <v>-3000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="J18" s="3">
         <v>-5200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="K18" s="3">
         <v>5100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="L18" s="3">
         <v>-200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="M18" s="3">
         <v>-2200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="N18" s="3">
         <v>-1500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="O18" s="3">
         <v>2700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="P18" s="3">
         <v>7300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="Q18" s="3">
         <v>4100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="R18" s="3">
         <v>500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="S18" s="3">
         <v>2800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="T18" s="3">
         <v>4600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="U18" s="3">
         <v>-1100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="V18" s="3">
         <v>-13300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="W18" s="3">
         <v>7400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="X18" s="3">
         <v>7100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Y18" s="3">
         <v>-2100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Z18" s="3">
         <v>-1900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="AA18" s="3">
         <v>5700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AB18" s="3">
         <v>5900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AC18" s="3">
         <v>5900</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-20400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AG18" s="3">
         <v>-17800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AH18" s="3">
         <v>-21900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AI18" s="3">
         <v>-11800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AJ18" s="3">
         <v>6300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AK18" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1783,151 +1881,163 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F20" s="3">
+        <v>7500</v>
+      </c>
+      <c r="G20" s="3">
         <v>-4800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="H20" s="3">
         <v>2600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="I20" s="3">
         <v>2600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="J20" s="3">
         <v>900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="L20" s="3">
         <v>1400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="N20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="O20" s="3">
         <v>-400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="P20" s="3">
         <v>1300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="Q20" s="3">
         <v>-1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="R20" s="3">
         <v>1800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="S20" s="3">
         <v>1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="T20" s="3">
         <v>700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="U20" s="3">
         <v>-2000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="V20" s="3">
         <v>1300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="W20" s="3">
         <v>-2500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="X20" s="3">
         <v>1800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="Y20" s="3">
         <v>-1200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Z20" s="3">
         <v>-800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="AA20" s="3">
         <v>500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AB20" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AC20" s="3">
         <v>1100</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AG20" s="3">
         <v>200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AH20" s="3">
         <v>7200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AI20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AJ20" s="3">
         <v>8100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AK20" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3">
         <v>-8400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="H21" s="3">
         <v>7100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="I21" s="3">
         <v>1700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="J21" s="3">
         <v>500</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3">
         <v>-700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="O21" s="3">
         <v>2300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="P21" s="3">
         <v>8400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="Q21" s="3">
         <v>4400</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1961,320 +2071,356 @@
       <c r="AB21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AG21" s="3">
         <v>3300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AH21" s="3">
         <v>9400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AI21" s="3">
         <v>5700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AJ21" s="3">
         <v>32500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AK21" s="3">
         <v>37200</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="D22" s="3">
         <v>500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="E22" s="3">
+        <v>400</v>
+      </c>
+      <c r="F22" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3">
+        <v>500</v>
+      </c>
+      <c r="K22" s="3">
         <v>1100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="L22" s="3">
         <v>800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="M22" s="3">
         <v>700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="N22" s="3">
         <v>1700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="O22" s="3">
         <v>1000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="P22" s="3">
         <v>1000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="Q22" s="3">
         <v>1500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="R22" s="3">
         <v>1400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="S22" s="3">
         <v>1500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="T22" s="3">
         <v>1700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="U22" s="3">
         <v>1600</v>
-      </c>
-      <c r="S22" s="3">
-        <v>2300</v>
-      </c>
-      <c r="T22" s="3">
-        <v>2200</v>
-      </c>
-      <c r="U22" s="3">
-        <v>2400</v>
       </c>
       <c r="V22" s="3">
         <v>2300</v>
       </c>
       <c r="W22" s="3">
+        <v>2200</v>
+      </c>
+      <c r="X22" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>2300</v>
+      </c>
+      <c r="Z22" s="3">
         <v>1900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="AA22" s="3">
         <v>2700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AB22" s="3">
         <v>2600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AC22" s="3">
         <v>1500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AD22" s="3">
         <v>3900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AE22" s="3">
         <v>1100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AF22" s="3">
         <v>8600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AG22" s="3">
         <v>9200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AH22" s="3">
         <v>7400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AI22" s="3">
         <v>8200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AJ22" s="3">
         <v>8500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AK22" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="G23" s="3">
         <v>-8800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="H23" s="3">
         <v>7600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="I23" s="3">
         <v>-400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="J23" s="3">
         <v>-4800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="K23" s="3">
         <v>3700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="L23" s="3">
         <v>400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="M23" s="3">
         <v>-1900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="N23" s="3">
         <v>-2700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="O23" s="3">
         <v>1300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="P23" s="3">
         <v>7500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="Q23" s="3">
         <v>1200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="R23" s="3">
         <v>900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="S23" s="3">
         <v>2500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="T23" s="3">
         <v>3700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="U23" s="3">
         <v>-4700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="V23" s="3">
         <v>-14300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="W23" s="3">
         <v>2700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="X23" s="3">
         <v>6600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="Y23" s="3">
         <v>-5500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Z23" s="3">
         <v>-4500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="AA23" s="3">
         <v>3600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AB23" s="3">
         <v>400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AC23" s="3">
         <v>5400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AD23" s="3">
         <v>3500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AE23" s="3">
         <v>4000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AF23" s="3">
         <v>-29100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AG23" s="3">
         <v>-26900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AH23" s="3">
         <v>-22100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AI23" s="3">
         <v>-22400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AJ23" s="3">
         <v>5900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AK23" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F24" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>300</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1300</v>
-      </c>
       <c r="H24" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3">
         <v>300</v>
       </c>
       <c r="J24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K24" s="3">
+        <v>200</v>
+      </c>
+      <c r="L24" s="3">
+        <v>300</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="W24" s="3">
         <v>800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-200</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>300</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF24" s="3">
         <v>2400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AG24" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AH24" s="3">
         <v>3400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AI24" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AJ24" s="3">
         <v>400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AK24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2371,204 +2517,231 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="G26" s="3">
         <v>-9000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="H26" s="3">
         <v>7700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="I26" s="3">
         <v>-600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="J26" s="3">
         <v>-6100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="K26" s="3">
         <v>3500</v>
       </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
         <v>-2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="N26" s="3">
         <v>-2900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="O26" s="3">
         <v>1100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="P26" s="3">
         <v>7600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="Q26" s="3">
         <v>800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="R26" s="3">
         <v>900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="S26" s="3">
         <v>2400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="T26" s="3">
         <v>3500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="U26" s="3">
         <v>-4700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="V26" s="3">
         <v>-14500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="W26" s="3">
         <v>1800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="X26" s="3">
         <v>6500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="Y26" s="3">
         <v>-5600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Z26" s="3">
         <v>-4300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="AA26" s="3">
         <v>3600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AB26" s="3">
         <v>400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AC26" s="3">
         <v>5400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AD26" s="3">
         <v>3200</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-31500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AG26" s="3">
         <v>-23200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AH26" s="3">
         <v>-25500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AI26" s="3">
         <v>-20500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AJ26" s="3">
         <v>5500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AK26" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G27" s="3">
         <v>-9400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="H27" s="3">
         <v>8300</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="H27" s="3">
-        <v>3000</v>
       </c>
       <c r="I27" s="3">
         <v>-200</v>
       </c>
       <c r="J27" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="K27" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M27" s="3">
         <v>-1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="N27" s="3">
         <v>-1600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="O27" s="3">
         <v>700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="P27" s="3">
         <v>7000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="Q27" s="3">
         <v>800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="R27" s="3">
         <v>2000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="S27" s="3">
         <v>2100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="T27" s="3">
         <v>3100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="U27" s="3">
         <v>-4400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="V27" s="3">
         <v>-10900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="W27" s="3">
         <v>2400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="X27" s="3">
         <v>5100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Y27" s="3">
         <v>-5400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Z27" s="3">
         <v>-4500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="AA27" s="3">
         <v>1500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AB27" s="3">
         <v>-700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AC27" s="3">
         <v>5400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AD27" s="3">
         <v>3200</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-31500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AG27" s="3">
         <v>-23200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AH27" s="3">
         <v>-25500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AI27" s="3">
         <v>-20500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AJ27" s="3">
         <v>5500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AK27" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2665,8 +2838,17 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2721,11 +2903,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2736,17 +2918,17 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -2763,8 +2945,17 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2861,8 +3052,17 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2959,204 +3159,231 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>400</v>
+      </c>
+      <c r="E32" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="G32" s="3">
         <v>4800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="H32" s="3">
         <v>-2600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="I32" s="3">
         <v>-2600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="J32" s="3">
         <v>-900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="L32" s="3">
         <v>-1400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="N32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="O32" s="3">
         <v>400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="P32" s="3">
         <v>-1300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="Q32" s="3">
         <v>1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="R32" s="3">
         <v>-1800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="S32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="T32" s="3">
         <v>-700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="U32" s="3">
         <v>2000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="V32" s="3">
         <v>-1300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="W32" s="3">
         <v>2500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="X32" s="3">
         <v>-1800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="Y32" s="3">
         <v>1200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Z32" s="3">
         <v>800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="AA32" s="3">
         <v>-500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AB32" s="3">
         <v>2800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AC32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF32" s="3">
         <v>100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AG32" s="3">
         <v>-200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AH32" s="3">
         <v>-7200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AI32" s="3">
         <v>2400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AJ32" s="3">
         <v>-8100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AK32" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G33" s="3">
         <v>-9400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="H33" s="3">
         <v>8300</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="H33" s="3">
-        <v>3000</v>
       </c>
       <c r="I33" s="3">
         <v>-200</v>
       </c>
       <c r="J33" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="K33" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M33" s="3">
         <v>-1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="N33" s="3">
         <v>-1600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="O33" s="3">
         <v>700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="P33" s="3">
         <v>7000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="Q33" s="3">
         <v>800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="R33" s="3">
         <v>2000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="S33" s="3">
         <v>2100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="T33" s="3">
         <v>3100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="U33" s="3">
         <v>-4400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="V33" s="3">
         <v>-10900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="W33" s="3">
         <v>2400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="X33" s="3">
         <v>5100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="Y33" s="3">
         <v>-5400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Z33" s="3">
         <v>-4500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="AA33" s="3">
         <v>1500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AB33" s="3">
         <v>-700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AC33" s="3">
         <v>5400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AD33" s="3">
         <v>3200</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-31500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AG33" s="3">
         <v>-23200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AH33" s="3">
         <v>-25500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AI33" s="3">
         <v>-20500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AJ33" s="3">
         <v>5500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AK33" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3253,209 +3480,236 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G35" s="3">
         <v>-9400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="H35" s="3">
         <v>8300</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="H35" s="3">
-        <v>3000</v>
       </c>
       <c r="I35" s="3">
         <v>-200</v>
       </c>
       <c r="J35" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="K35" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M35" s="3">
         <v>-1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="N35" s="3">
         <v>-1600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="O35" s="3">
         <v>700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="P35" s="3">
         <v>7000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="Q35" s="3">
         <v>800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="R35" s="3">
         <v>2000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="S35" s="3">
         <v>2100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="T35" s="3">
         <v>3100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="U35" s="3">
         <v>-4400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="V35" s="3">
         <v>-10900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="W35" s="3">
         <v>2400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="X35" s="3">
         <v>5100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="Y35" s="3">
         <v>-5400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Z35" s="3">
         <v>-4500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="AA35" s="3">
         <v>1500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AB35" s="3">
         <v>-700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AC35" s="3">
         <v>5400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AD35" s="3">
         <v>3200</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-31500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AG35" s="3">
         <v>-23200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AH35" s="3">
         <v>-25500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AI35" s="3">
         <v>-20500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AJ35" s="3">
         <v>5500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AK35" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AJ38" s="2">
         <v>42551</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AK38" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3490,8 +3744,11 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3526,141 +3783,153 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>55100</v>
+      </c>
+      <c r="F41" s="3">
+        <v>70200</v>
+      </c>
+      <c r="G41" s="3">
         <v>59200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="H41" s="3">
         <v>60500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
         <v>66700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="J41" s="3">
         <v>107100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="K41" s="3">
         <v>123000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="L41" s="3">
         <v>207900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>222900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>254100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="O41" s="3">
         <v>275400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3">
         <v>286000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="Q41" s="3">
         <v>301000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="R41" s="3">
         <v>40600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="S41" s="3">
         <v>15600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="T41" s="3">
         <v>11300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="U41" s="3">
         <v>15500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="V41" s="3">
         <v>24300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="W41" s="3">
         <v>9400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="X41" s="3">
         <v>8700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="Y41" s="3">
         <v>7000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Z41" s="3">
         <v>6800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="AA41" s="3">
         <v>8100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AB41" s="3">
         <v>24800</v>
       </c>
-      <c r="Z41" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="3">
         <v>13400</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF41" s="3">
         <v>28600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AG41" s="3">
         <v>26600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AH41" s="3">
         <v>37300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AI41" s="3">
         <v>28800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AJ41" s="3">
         <v>23700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AK41" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42" s="3">
         <v>10100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="H42" s="3">
         <v>10100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="I42" s="3">
         <v>10000</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J42" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -3722,106 +3991,124 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>75800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>84200</v>
+      </c>
+      <c r="F43" s="3">
+        <v>93800</v>
+      </c>
+      <c r="G43" s="3">
         <v>76500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="H43" s="3">
         <v>86400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="I43" s="3">
         <v>79100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="J43" s="3">
         <v>71500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="K43" s="3">
         <v>52700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="L43" s="3">
         <v>39400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3">
         <v>46700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <v>50400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="O43" s="3">
         <v>48300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="P43" s="3">
         <v>39600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="Q43" s="3">
         <v>36000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="R43" s="3">
         <v>23800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="S43" s="3">
         <v>24700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="T43" s="3">
         <v>29500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="U43" s="3">
         <v>21000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="V43" s="3">
         <v>21300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="W43" s="3">
         <v>46600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="X43" s="3">
         <v>49300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="Y43" s="3">
         <v>50700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Z43" s="3">
         <v>47300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="AA43" s="3">
         <v>55900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AB43" s="3">
         <v>58900</v>
       </c>
-      <c r="Z43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="3">
         <v>38500</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF43" s="3">
         <v>134000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AG43" s="3">
         <v>129700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AH43" s="3">
         <v>134100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AI43" s="3">
         <v>204000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AJ43" s="3">
         <v>195900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AK43" s="3">
         <v>199000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3882,272 +4169,299 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>8</v>
+      <c r="W44" s="3">
+        <v>0</v>
       </c>
       <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA44" s="3">
         <v>200</v>
       </c>
-      <c r="Y44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC44" s="3">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF44" s="3">
         <v>92300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AG44" s="3">
         <v>153200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AH44" s="3">
         <v>144000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AI44" s="3">
         <v>185200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AJ44" s="3">
         <v>165500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AK44" s="3">
         <v>181700</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>91200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>79700</v>
+      </c>
+      <c r="F45" s="3">
+        <v>62500</v>
+      </c>
+      <c r="G45" s="3">
         <v>67800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="H45" s="3">
         <v>72200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="I45" s="3">
         <v>54900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="J45" s="3">
         <v>42100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="K45" s="3">
         <v>36000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="L45" s="3">
         <v>38400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="M45" s="3">
         <v>38800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="N45" s="3">
         <v>24700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="O45" s="3">
         <v>27500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="P45" s="3">
         <v>31500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="Q45" s="3">
         <v>33200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="R45" s="3">
         <v>72300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="S45" s="3">
         <v>32300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="T45" s="3">
         <v>27600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="U45" s="3">
         <v>47700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="V45" s="3">
         <v>57400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="W45" s="3">
         <v>50800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="X45" s="3">
         <v>80900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="Y45" s="3">
         <v>80500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Z45" s="3">
         <v>81200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="AA45" s="3">
         <v>73800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AB45" s="3">
         <v>91600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AC45" s="3">
         <v>100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AD45" s="3">
         <v>118100</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF45" s="3">
         <v>264300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AG45" s="3">
         <v>233600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AH45" s="3">
         <v>192100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AI45" s="3">
         <v>194500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AJ45" s="3">
         <v>248100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AK45" s="3">
         <v>232700</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>217900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>218900</v>
+      </c>
+      <c r="F46" s="3">
+        <v>226500</v>
+      </c>
+      <c r="G46" s="3">
         <v>213500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="H46" s="3">
         <v>229100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
         <v>210700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="J46" s="3">
         <v>220700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="K46" s="3">
         <v>211700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="L46" s="3">
         <v>285700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
         <v>308400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>329200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="O46" s="3">
         <v>351200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="P46" s="3">
         <v>357100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="Q46" s="3">
         <v>370200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="R46" s="3">
         <v>136700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="S46" s="3">
         <v>72500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="T46" s="3">
         <v>68400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="U46" s="3">
         <v>84200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="V46" s="3">
         <v>103100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="W46" s="3">
         <v>106800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="X46" s="3">
         <v>138900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="Y46" s="3">
         <v>138200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Z46" s="3">
         <v>135300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="AA46" s="3">
         <v>138000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AB46" s="3">
         <v>175300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AC46" s="3">
         <v>200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AD46" s="3">
         <v>170100</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF46" s="3">
         <v>519200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AG46" s="3">
         <v>543200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AH46" s="3">
         <v>507500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AI46" s="3">
         <v>612500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AJ46" s="3">
         <v>633100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AK46" s="3">
         <v>652100</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G47" s="3">
-        <v>10000</v>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H47" s="3">
-        <v>10000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>10000</v>
+        <v>0</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J47" s="3">
         <v>10000</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
+      <c r="K47" s="3">
+        <v>10000</v>
+      </c>
+      <c r="L47" s="3">
+        <v>10000</v>
+      </c>
+      <c r="M47" s="3">
+        <v>10000</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
@@ -4158,14 +4472,14 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3">
-        <v>0</v>
-      </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -4212,120 +4526,138 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>185200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>185900</v>
+      </c>
+      <c r="F48" s="3">
+        <v>198400</v>
+      </c>
+      <c r="G48" s="3">
         <v>189100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="H48" s="3">
         <v>192800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
         <v>216500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="J48" s="3">
         <v>214800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
         <v>202700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="L48" s="3">
         <v>160600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
         <v>166300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <v>167100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="O48" s="3">
         <v>167300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3">
         <v>167300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="Q48" s="3">
         <v>166200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="R48" s="3">
         <v>168700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="S48" s="3">
         <v>186900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="T48" s="3">
         <v>183200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="U48" s="3">
         <v>187500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="V48" s="3">
         <v>192300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="W48" s="3">
         <v>211400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="X48" s="3">
         <v>249000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="Y48" s="3">
         <v>226100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Z48" s="3">
         <v>190800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="AA48" s="3">
         <v>192500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AB48" s="3">
         <v>195900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AC48" s="3">
         <v>200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AD48" s="3">
         <v>154700</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF48" s="3">
         <v>537600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AG48" s="3">
         <v>486300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AH48" s="3">
         <v>491300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AI48" s="3">
         <v>547700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AJ48" s="3">
         <v>568100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AK48" s="3">
         <v>603200</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3">
-        <v>1000</v>
+      <c r="D49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F49" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
         <v>1000</v>
@@ -4351,14 +4683,14 @@
       <c r="O49" s="3">
         <v>1000</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>8</v>
+      <c r="P49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R49" s="3">
+        <v>1000</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>8</v>
@@ -4369,14 +4701,14 @@
       <c r="U49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
-      </c>
-      <c r="W49" s="3">
-        <v>0</v>
-      </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
@@ -4384,32 +4716,41 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB49" s="3" t="s">
-        <v>8</v>
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="3">
+        <v>0</v>
       </c>
       <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF49" s="3">
         <v>32200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AG49" s="3">
         <v>31900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AH49" s="3">
         <v>31900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AI49" s="3">
         <v>35500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AJ49" s="3">
         <v>35800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AK49" s="3">
         <v>37200</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4506,8 +4847,17 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4604,106 +4954,124 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>51800</v>
+        <v>54700</v>
       </c>
       <c r="E52" s="3">
-        <v>54700</v>
+        <v>58700</v>
       </c>
       <c r="F52" s="3">
         <v>53500</v>
       </c>
       <c r="G52" s="3">
+        <v>51800</v>
+      </c>
+      <c r="H52" s="3">
+        <v>54700</v>
+      </c>
+      <c r="I52" s="3">
+        <v>53500</v>
+      </c>
+      <c r="J52" s="3">
         <v>47200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="K52" s="3">
         <v>41800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="L52" s="3">
         <v>42900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="M52" s="3">
         <v>34200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="N52" s="3">
         <v>31900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="O52" s="3">
         <v>36400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="P52" s="3">
         <v>33800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="Q52" s="3">
         <v>29700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="R52" s="3">
         <v>30400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="S52" s="3">
         <v>29700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="T52" s="3">
         <v>26500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="U52" s="3">
         <v>25300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="V52" s="3">
         <v>24600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="W52" s="3">
         <v>14500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="X52" s="3">
         <v>18400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="Y52" s="3">
         <v>53400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Z52" s="3">
         <v>51700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="AA52" s="3">
         <v>44900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AB52" s="3">
         <v>18500</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="3">
         <v>11000</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF52" s="3">
         <v>66000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AG52" s="3">
         <v>65000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AH52" s="3">
         <v>57800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AI52" s="3">
         <v>50800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AJ52" s="3">
         <v>51700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AK52" s="3">
         <v>46400</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4800,106 +5168,124 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>457800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>463500</v>
+      </c>
+      <c r="F54" s="3">
+        <v>478400</v>
+      </c>
+      <c r="G54" s="3">
         <v>454400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>477700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
         <v>481700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="J54" s="3">
         <v>493900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="K54" s="3">
         <v>467200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>500300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>519900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>529300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>556000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>559200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="Q54" s="3">
         <v>567100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="R54" s="3">
         <v>336900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="S54" s="3">
         <v>289100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="T54" s="3">
         <v>278000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="U54" s="3">
         <v>296900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="V54" s="3">
         <v>319900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="W54" s="3">
         <v>332700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="X54" s="3">
         <v>406300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="Y54" s="3">
         <v>417700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Z54" s="3">
         <v>377700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="AA54" s="3">
         <v>375400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AB54" s="3">
         <v>389600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AC54" s="3">
         <v>400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AD54" s="3">
         <v>335700</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF54" s="3">
         <v>1154900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AG54" s="3">
         <v>1126300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AH54" s="3">
         <v>1088400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AI54" s="3">
         <v>1246600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AJ54" s="3">
         <v>1288700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AK54" s="3">
         <v>1338900</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4934,8 +5320,11 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,596 +5359,653 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>18500</v>
+      </c>
+      <c r="F57" s="3">
+        <v>16200</v>
+      </c>
+      <c r="G57" s="3">
         <v>3100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="H57" s="3">
         <v>5400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="I57" s="3">
         <v>5900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="J57" s="3">
         <v>7100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="K57" s="3">
         <v>6500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="L57" s="3">
         <v>2700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="M57" s="3">
         <v>4200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="N57" s="3">
         <v>3800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="O57" s="3">
         <v>4700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="P57" s="3">
         <v>4100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="Q57" s="3">
         <v>4600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="R57" s="3">
         <v>6300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="S57" s="3">
         <v>9800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="T57" s="3">
         <v>6700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="U57" s="3">
         <v>6900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="V57" s="3">
         <v>20400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="W57" s="3">
         <v>14000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="X57" s="3">
         <v>10800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="Y57" s="3">
         <v>12500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Z57" s="3">
         <v>12100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="AA57" s="3">
         <v>24600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AB57" s="3">
         <v>23700</v>
       </c>
-      <c r="Z57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="3">
         <v>25800</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF57" s="3">
         <v>203200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AG57" s="3">
         <v>221600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AH57" s="3">
         <v>223300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AI57" s="3">
         <v>281300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AJ57" s="3">
         <v>280600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AK57" s="3">
         <v>302000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F58" s="3">
+        <v>5900</v>
+      </c>
+      <c r="G58" s="3">
         <v>6000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="H58" s="3">
         <v>6700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="I58" s="3">
         <v>9900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="J58" s="3">
         <v>11000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="K58" s="3">
         <v>10000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="L58" s="3">
         <v>10700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="M58" s="3">
         <v>12200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="N58" s="3">
         <v>11400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="O58" s="3">
         <v>12300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="P58" s="3">
         <v>12800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="Q58" s="3">
         <v>23000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="R58" s="3">
         <v>49100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="S58" s="3">
         <v>43500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="T58" s="3">
         <v>42100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="U58" s="3">
         <v>43900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="V58" s="3">
         <v>47800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="W58" s="3">
         <v>57100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="X58" s="3">
         <v>108900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="Y58" s="3">
         <v>101900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Z58" s="3">
         <v>44500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="AA58" s="3">
         <v>7100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AB58" s="3">
         <v>15100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AC58" s="3">
         <v>23700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AD58" s="3">
         <v>6600</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF58" s="3">
         <v>671400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AG58" s="3">
         <v>647600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AH58" s="3">
         <v>595400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AI58" s="3">
         <v>699000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AJ58" s="3">
         <v>716500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AK58" s="3">
         <v>735600</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>33700</v>
+      </c>
+      <c r="F59" s="3">
+        <v>34800</v>
+      </c>
+      <c r="G59" s="3">
         <v>30400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="H59" s="3">
         <v>29800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="I59" s="3">
         <v>27900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="J59" s="3">
         <v>25200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="K59" s="3">
         <v>17400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="L59" s="3">
         <v>17700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
         <v>17400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="N59" s="3">
         <v>20000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="O59" s="3">
         <v>19300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="P59" s="3">
         <v>19600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="Q59" s="3">
         <v>23500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="R59" s="3">
         <v>32900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="S59" s="3">
         <v>19900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="T59" s="3">
         <v>27000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="U59" s="3">
         <v>38600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="V59" s="3">
         <v>41100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="W59" s="3">
         <v>42400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="X59" s="3">
         <v>43100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="Y59" s="3">
         <v>56500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Z59" s="3">
         <v>77200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="AA59" s="3">
         <v>61600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AB59" s="3">
         <v>73500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AC59" s="3">
         <v>100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AD59" s="3">
         <v>112800</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF59" s="3">
         <v>150800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AG59" s="3">
         <v>101600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AH59" s="3">
         <v>85700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AI59" s="3">
         <v>82600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AJ59" s="3">
         <v>89900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AK59" s="3">
         <v>91500</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>57700</v>
+      </c>
+      <c r="F60" s="3">
+        <v>57000</v>
+      </c>
+      <c r="G60" s="3">
         <v>39500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="H60" s="3">
         <v>41800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
         <v>43700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="J60" s="3">
         <v>43300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="K60" s="3">
         <v>34000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="L60" s="3">
         <v>31100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
         <v>33800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="N60" s="3">
         <v>35100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="O60" s="3">
         <v>36400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="P60" s="3">
         <v>36500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="Q60" s="3">
         <v>51100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="R60" s="3">
         <v>88300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="S60" s="3">
         <v>73200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="T60" s="3">
         <v>75900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="U60" s="3">
         <v>89400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="V60" s="3">
         <v>109400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="W60" s="3">
         <v>113500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="X60" s="3">
         <v>162800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="Y60" s="3">
         <v>170900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Z60" s="3">
         <v>133700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="AA60" s="3">
         <v>93300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AB60" s="3">
         <v>104700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AC60" s="3">
         <v>200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AD60" s="3">
         <v>145200</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF60" s="3">
         <v>1025400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AG60" s="3">
         <v>970800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AH60" s="3">
         <v>904400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AI60" s="3">
         <v>1062900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AJ60" s="3">
         <v>1087000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AK60" s="3">
         <v>1129100</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>33600</v>
+      </c>
+      <c r="F61" s="3">
+        <v>33900</v>
+      </c>
+      <c r="G61" s="3">
         <v>33300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="H61" s="3">
         <v>35400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="I61" s="3">
         <v>37400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="J61" s="3">
         <v>37500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="K61" s="3">
         <v>38000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="L61" s="3">
         <v>21200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="M61" s="3">
         <v>26900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="N61" s="3">
         <v>30000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="O61" s="3">
         <v>31700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="P61" s="3">
         <v>36100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="Q61" s="3">
         <v>38800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="R61" s="3">
         <v>44000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="S61" s="3">
         <v>48100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="T61" s="3">
         <v>44800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="U61" s="3">
         <v>52500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="V61" s="3">
         <v>50100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="W61" s="3">
         <v>68400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="X61" s="3">
         <v>81200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="Y61" s="3">
         <v>89100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Z61" s="3">
         <v>119300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="AA61" s="3">
         <v>153200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AB61" s="3">
         <v>157800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AC61" s="3">
         <v>100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AD61" s="3">
         <v>32500</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>30300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AG61" s="3">
         <v>31100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AH61" s="3">
         <v>28800</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>21000</v>
+        <v>23900</v>
       </c>
       <c r="E62" s="3">
-        <v>21600</v>
+        <v>23600</v>
       </c>
       <c r="F62" s="3">
         <v>24100</v>
       </c>
       <c r="G62" s="3">
+        <v>21000</v>
+      </c>
+      <c r="H62" s="3">
+        <v>21600</v>
+      </c>
+      <c r="I62" s="3">
+        <v>24100</v>
+      </c>
+      <c r="J62" s="3">
         <v>24400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="K62" s="3">
         <v>15500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="L62" s="3">
         <v>15400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="M62" s="3">
         <v>15500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="N62" s="3">
         <v>15800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="O62" s="3">
         <v>19500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="P62" s="3">
         <v>19700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="Q62" s="3">
         <v>20100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="R62" s="3">
         <v>21400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="S62" s="3">
         <v>20400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="T62" s="3">
         <v>21200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="U62" s="3">
         <v>22600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="V62" s="3">
         <v>22900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="W62" s="3">
         <v>21500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="X62" s="3">
         <v>33600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="Y62" s="3">
         <v>35300</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA62" s="3">
+      <c r="Z62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="3">
         <v>67500</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF62" s="3">
         <v>84400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AG62" s="3">
         <v>82600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AH62" s="3">
         <v>89000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AI62" s="3">
         <v>92000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AJ62" s="3">
         <v>89500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AK62" s="3">
         <v>93600</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5656,8 +6102,17 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5754,8 +6209,17 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5852,106 +6316,124 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>152600</v>
+      </c>
+      <c r="F66" s="3">
+        <v>153000</v>
+      </c>
+      <c r="G66" s="3">
         <v>132100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="H66" s="3">
         <v>137200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
         <v>146000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="J66" s="3">
         <v>146600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="K66" s="3">
         <v>128100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="L66" s="3">
         <v>110100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
         <v>120400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>125300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="O66" s="3">
         <v>133000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>137200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="Q66" s="3">
         <v>153800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="R66" s="3">
         <v>197800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="S66" s="3">
         <v>185700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="T66" s="3">
         <v>184400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="U66" s="3">
         <v>206600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="V66" s="3">
         <v>225200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="W66" s="3">
         <v>238300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="X66" s="3">
         <v>313900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="Y66" s="3">
         <v>329600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Z66" s="3">
         <v>287000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="AA66" s="3">
         <v>280700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AB66" s="3">
         <v>294400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AC66" s="3">
         <v>300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AD66" s="3">
         <v>245200</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF66" s="3">
         <v>1141000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AG66" s="3">
         <v>1084400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AH66" s="3">
         <v>1022300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AI66" s="3">
         <v>1154900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AJ66" s="3">
         <v>1176400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AK66" s="3">
         <v>1224200</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5986,8 +6468,11 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6084,8 +6569,17 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6182,8 +6676,17 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6280,8 +6783,17 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6378,106 +6890,124 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-446100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-446500</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-440600</v>
+      </c>
+      <c r="G72" s="3">
         <v>-438600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="H72" s="3">
         <v>-429200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="I72" s="3">
         <v>-437600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="J72" s="3">
         <v>-437400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="K72" s="3">
         <v>-431600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="L72" s="3">
         <v>-434600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>-434400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>-432700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="O72" s="3">
         <v>-431100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="P72" s="3">
         <v>-431800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="Q72" s="3">
         <v>-438800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="R72" s="3">
         <v>-439600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="S72" s="3">
         <v>-441500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="T72" s="3">
         <v>-443700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="U72" s="3">
         <v>-446700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="V72" s="3">
         <v>-442300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="W72" s="3">
         <v>-431400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="X72" s="3">
         <v>-433800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="Y72" s="3">
         <v>-438900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Z72" s="3">
         <v>-433500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="AA72" s="3">
         <v>-428400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AB72" s="3">
         <v>-429900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AC72" s="3">
         <v>-400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AD72" s="3">
         <v>-435500</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF72" s="3">
         <v>-524700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AG72" s="3">
         <v>-493200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AH72" s="3">
         <v>-470000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AI72" s="3">
         <v>-444500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AJ72" s="3">
         <v>-424000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AK72" s="3">
         <v>-429500</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6574,8 +7104,17 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6672,8 +7211,17 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6770,106 +7318,124 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>309700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>311000</v>
+      </c>
+      <c r="F76" s="3">
+        <v>325300</v>
+      </c>
+      <c r="G76" s="3">
         <v>322300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>340500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
         <v>335700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="J76" s="3">
         <v>347300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="K76" s="3">
         <v>339100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="L76" s="3">
         <v>390200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>399500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>404000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>422900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>422000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="Q76" s="3">
         <v>413300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="R76" s="3">
         <v>139100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="S76" s="3">
         <v>103300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="T76" s="3">
         <v>93600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="U76" s="3">
         <v>90300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="V76" s="3">
         <v>94700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="W76" s="3">
         <v>94400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="X76" s="3">
         <v>92400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="Y76" s="3">
         <v>88100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Z76" s="3">
         <v>90700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="AA76" s="3">
         <v>94800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AB76" s="3">
         <v>95200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AC76" s="3">
         <v>100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AD76" s="3">
         <v>90500</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF76" s="3">
         <v>13900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AG76" s="3">
         <v>41900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AH76" s="3">
         <v>66100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AI76" s="3">
         <v>91700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AJ76" s="3">
         <v>112300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AK76" s="3">
         <v>114700</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6966,209 +7532,236 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AJ80" s="2">
         <v>42551</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AK80" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G81" s="3">
         <v>-9400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="H81" s="3">
         <v>8300</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="H81" s="3">
-        <v>3000</v>
       </c>
       <c r="I81" s="3">
         <v>-200</v>
       </c>
       <c r="J81" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="K81" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M81" s="3">
         <v>-1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="N81" s="3">
         <v>-1600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="O81" s="3">
         <v>700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="P81" s="3">
         <v>7000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="Q81" s="3">
         <v>800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="R81" s="3">
         <v>2000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="S81" s="3">
         <v>2100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="T81" s="3">
         <v>3100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="U81" s="3">
         <v>-4400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="V81" s="3">
         <v>-10900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="W81" s="3">
         <v>2400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="X81" s="3">
         <v>5100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="Y81" s="3">
         <v>-5400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Z81" s="3">
         <v>-4500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="AA81" s="3">
         <v>1500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AB81" s="3">
         <v>-700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AC81" s="3">
         <v>5400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AD81" s="3">
         <v>3200</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-31500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AG81" s="3">
         <v>-23200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AH81" s="3">
         <v>-25500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AI81" s="3">
         <v>-20500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AJ81" s="3">
         <v>5500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AK81" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7203,31 +7796,34 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+        <v>1800</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7274,35 +7870,44 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>8</v>
+      <c r="Z83" s="3">
+        <v>0</v>
       </c>
       <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD83" s="3">
         <v>4500</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF83" s="3">
         <v>17800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AG83" s="3">
         <v>20900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AH83" s="3">
         <v>24100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AI83" s="3">
         <v>19900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AJ83" s="3">
         <v>18100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AK83" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7399,8 +8004,17 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7497,8 +8111,17 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7595,8 +8218,17 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7693,8 +8325,17 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7791,65 +8432,74 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="F89" s="3">
+        <v>7200</v>
+      </c>
+      <c r="G89" s="3">
         <v>-4600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="H89" s="3">
         <v>-2400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="I89" s="3">
         <v>-23700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="J89" s="3">
         <v>-10600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="K89" s="3">
         <v>-5200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="L89" s="3">
         <v>-7900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3">
         <v>-14400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>8800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="O89" s="3">
         <v>-5100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="P89" s="3">
         <v>600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="Q89" s="3">
         <v>-10500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="R89" s="3">
         <v>-3600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="S89" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="T89" s="3">
         <v>5300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="U89" s="3">
         <v>-9900</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>8</v>
       </c>
@@ -7859,38 +8509,47 @@
       <c r="X89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
+      <c r="Y89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD89" s="3">
         <v>18400</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AG89" s="3">
         <v>-33800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AH89" s="3">
         <v>44600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AI89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AJ89" s="3">
         <v>-9100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AK89" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7925,13 +8584,16 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-3900</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -7996,35 +8658,44 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>8</v>
+      <c r="Z91" s="3">
+        <v>0</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-80300</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-11300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AG91" s="3">
         <v>-11400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AH91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AI91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AJ91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AK91" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8121,8 +8792,17 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8219,65 +8899,74 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F94" s="3">
+        <v>6900</v>
+      </c>
+      <c r="G94" s="3">
         <v>10100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="H94" s="3">
         <v>100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="I94" s="3">
         <v>-1900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="J94" s="3">
         <v>-7600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="K94" s="3">
         <v>-31200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="L94" s="3">
         <v>-2000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="M94" s="3">
         <v>-3700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="N94" s="3">
         <v>-3100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="O94" s="3">
         <v>-3000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="P94" s="3">
         <v>-800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="Q94" s="3">
         <v>26100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="R94" s="3">
         <v>-3700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="S94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="T94" s="3">
         <v>100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="U94" s="3">
         <v>1200</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>8</v>
       </c>
@@ -8287,38 +8976,47 @@
       <c r="X94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-156400</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AG94" s="3">
         <v>-30100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AH94" s="3">
         <v>17900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AI94" s="3">
         <v>26000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AJ94" s="3">
         <v>5200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AK94" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8353,8 +9051,11 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8451,8 +9152,17 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8549,8 +9259,17 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8647,8 +9366,17 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8745,65 +9473,74 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="G100" s="3">
         <v>-6700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="H100" s="3">
         <v>1200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="I100" s="3">
         <v>-16200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="J100" s="3">
         <v>4600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="K100" s="3">
         <v>-45700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="L100" s="3">
         <v>-4900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="M100" s="3">
         <v>-14200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="N100" s="3">
         <v>-23700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="O100" s="3">
         <v>-2200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="P100" s="3">
         <v>-14300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="Q100" s="3">
         <v>244800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="R100" s="3">
         <v>32600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="S100" s="3">
         <v>8300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="T100" s="3">
         <v>-9400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="U100" s="3">
         <v>-1400</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>8</v>
       </c>
@@ -8813,95 +9550,104 @@
       <c r="X100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
+      <c r="Y100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD100" s="3">
         <v>102400</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF100" s="3">
         <v>16000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AG100" s="3">
         <v>50700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AH100" s="3">
         <v>-48900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AI100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AJ100" s="3">
         <v>-4200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AK100" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E101" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F101" s="3">
+        <v>400</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-5200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="I101" s="3">
         <v>1200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="J101" s="3">
         <v>-2100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="K101" s="3">
         <v>-3000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="M101" s="3">
         <v>800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="N101" s="3">
         <v>-3400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="Q101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="R101" s="3">
         <v>-1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="S101" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="T101" s="3">
         <v>-600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="U101" s="3">
         <v>1900</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>8</v>
       </c>
@@ -8911,95 +9657,104 @@
       <c r="X101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="Y101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AA101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD101" s="3">
         <v>11600</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AG101" s="3">
         <v>2500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AH101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AI101" s="3">
         <v>2400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AJ101" s="3">
         <v>-6800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AK101" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="F102" s="3">
+        <v>11000</v>
+      </c>
+      <c r="G102" s="3">
         <v>-1300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="H102" s="3">
         <v>-6300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="I102" s="3">
         <v>-40600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="J102" s="3">
         <v>-15700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="K102" s="3">
         <v>-85000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="L102" s="3">
         <v>-14900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="M102" s="3">
         <v>-31500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="N102" s="3">
         <v>-21500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="O102" s="3">
         <v>-10200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="P102" s="3">
         <v>-15000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="Q102" s="3">
         <v>260300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="R102" s="3">
         <v>24300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="S102" s="3">
         <v>4300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="T102" s="3">
         <v>-4500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="U102" s="3">
         <v>-8100</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>8</v>
       </c>
@@ -9009,34 +9764,43 @@
       <c r="X102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
+      <c r="Y102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-23900</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF102" s="3">
         <v>2000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AG102" s="3">
         <v>-10700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AH102" s="3">
         <v>8500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AI102" s="3">
         <v>5100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AJ102" s="3">
         <v>-15000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AK102" s="3">
         <v>600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
   <si>
     <t>SOL</t>
   </si>
@@ -656,480 +656,493 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42551</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E8" s="3">
         <v>30100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>45000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>33800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>28900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>22800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>18500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>22800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>16400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>9700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>26200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>21200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>26500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>66000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>13600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>13100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>18800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>27800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>44800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>103000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>36300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>151600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>156600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>232100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>187000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>250000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>260700</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E9" s="3">
         <v>20700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>39900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>21200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>11300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>20300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>16000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>14400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>18800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>19800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>19400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>49700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>12700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>10200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>19600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>36400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>88800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>29900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>147500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>154900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>227100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>168200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>208900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>216200</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E10" s="3">
         <v>9400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5100</v>
       </c>
-      <c r="G10" s="3">
-        <v>5600</v>
-      </c>
       <c r="H10" s="3">
-        <v>12600</v>
+        <v>5700</v>
       </c>
       <c r="I10" s="3">
+        <v>12700</v>
+      </c>
+      <c r="J10" s="3">
         <v>1600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>7200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>7400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>7100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>16300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>10500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>14200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>6400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>5000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>18800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>41100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>44500</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1167,8 +1180,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1256,26 +1270,29 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG12" s="3">
         <v>5400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>5700</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>5400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>6300</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>7400</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,82 +1398,85 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F14" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+        <v>900</v>
+      </c>
+      <c r="G14" s="3">
+        <v>4200</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1300</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>400</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>300</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>1000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>5500</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
@@ -1464,8 +1484,8 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1473,46 +1493,49 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH14" s="3">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI14" s="3">
         <v>4700</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1595,8 +1618,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,222 +1657,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E17" s="3">
         <v>27100</v>
       </c>
-      <c r="E17" s="3">
-        <v>15800</v>
-      </c>
       <c r="F17" s="3">
-        <v>51700</v>
+        <v>14900</v>
       </c>
       <c r="G17" s="3">
-        <v>17900</v>
+        <v>47500</v>
       </c>
       <c r="H17" s="3">
+        <v>16600</v>
+      </c>
+      <c r="I17" s="3">
         <v>28800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>25900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>21600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>22300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>39800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>58600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>15200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>13100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>21900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>38900</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AF17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG17" s="3">
         <v>172000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>174400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>254000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>198800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>243700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>248200</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E18" s="3">
         <v>3000</v>
       </c>
-      <c r="E18" s="3">
-        <v>-1200</v>
-      </c>
       <c r="F18" s="3">
-        <v>-6700</v>
+        <v>-300</v>
       </c>
       <c r="G18" s="3">
-        <v>-4000</v>
+        <v>-2600</v>
       </c>
       <c r="H18" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I18" s="3">
         <v>5000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-13300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>7400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>7100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>5700</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>5900</v>
       </c>
       <c r="AC18" s="3">
         <v>5900</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>8</v>
+      <c r="AD18" s="3">
+        <v>5900</v>
       </c>
       <c r="AE18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-20400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-17800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-21900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-11800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>6300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,163 +1917,167 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>800</v>
+      </c>
+      <c r="F20" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="H20" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="K20" s="3">
+        <v>900</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O20" s="3">
+        <v>500</v>
+      </c>
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="E20" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="F20" s="3">
-        <v>7500</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="H20" s="3">
-        <v>2600</v>
-      </c>
-      <c r="I20" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J20" s="3">
-        <v>900</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L20" s="3">
-        <v>1400</v>
-      </c>
-      <c r="M20" s="3">
-        <v>1000</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="Q20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="R20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="S20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="T20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="U20" s="3">
+        <v>700</v>
+      </c>
+      <c r="V20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="W20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="X20" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AB20" s="3">
         <v>500</v>
       </c>
-      <c r="O20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="P20" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="R20" s="3">
-        <v>1800</v>
-      </c>
-      <c r="S20" s="3">
-        <v>1200</v>
-      </c>
-      <c r="T20" s="3">
-        <v>700</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="V20" s="3">
-        <v>1300</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="X20" s="3">
-        <v>1800</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>500</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1100</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AF20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>7200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>8100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4100</v>
+        <v>8500</v>
       </c>
       <c r="E21" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>8</v>
+        <v>3600</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-1800</v>
       </c>
       <c r="G21" s="3">
-        <v>-8400</v>
+        <v>5300</v>
       </c>
       <c r="H21" s="3">
-        <v>7100</v>
+        <v>-5600</v>
       </c>
       <c r="I21" s="3">
-        <v>1700</v>
+        <v>8700</v>
       </c>
       <c r="J21" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K21" s="3">
         <v>500</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="3">
         <v>-700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4400</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2080,315 +2117,324 @@
       <c r="AE21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG21" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>9400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>5700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>32500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>37200</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>700</v>
+      </c>
+      <c r="E22" s="3">
         <v>500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>400</v>
       </c>
-      <c r="F22" s="3">
-        <v>2200</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
+      <c r="G22" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H22" s="3">
+        <v>500</v>
+      </c>
+      <c r="I22" s="3">
+        <v>200</v>
       </c>
       <c r="J22" s="3">
+        <v>700</v>
+      </c>
+      <c r="K22" s="3">
         <v>500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1700</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1000</v>
       </c>
       <c r="P22" s="3">
         <v>1000</v>
       </c>
       <c r="Q22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R22" s="3">
         <v>1500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>3900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>8600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>9200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>7400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>8200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>8500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E23" s="3">
         <v>2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-14300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>5400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-29100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-26900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-22100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-22400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>5900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>1300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-200</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
         <v>0</v>
       </c>
@@ -2396,31 +2442,34 @@
         <v>0</v>
       </c>
       <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>300</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF24" s="3">
+      <c r="AF24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG24" s="3">
         <v>2400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-3600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-1900</v>
-      </c>
-      <c r="AJ24" s="3">
-        <v>400</v>
       </c>
       <c r="AK24" s="3">
         <v>400</v>
       </c>
+      <c r="AL24" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,222 +2575,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E26" s="3">
         <v>700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3500</v>
       </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
       <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
         <v>-2000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-14500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>6500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-5600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>5400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3200</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF26" s="3">
+      <c r="AF26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG26" s="3">
         <v>-31500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-23200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-25500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-20500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>5500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E27" s="3">
         <v>400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-10900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>5400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3200</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF27" s="3">
+      <c r="AF27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-31500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-23200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-25500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-20500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>5500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +2905,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2912,17 +2973,17 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2930,8 +2991,8 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE29" s="3">
         <v>0</v>
@@ -2954,8 +3015,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3125,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,222 +3235,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="G32" s="3">
+        <v>5900</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="I32" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L32" s="3">
+        <v>200</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="E32" s="3">
-        <v>2700</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-7500</v>
-      </c>
-      <c r="G32" s="3">
-        <v>4800</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="K32" s="3">
-        <v>200</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="Q32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="R32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="T32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="U32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="V32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="W32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="X32" s="3">
+        <v>2500</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-500</v>
       </c>
-      <c r="O32" s="3">
-        <v>400</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>1400</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="U32" s="3">
-        <v>2000</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="W32" s="3">
-        <v>2500</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>1200</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>800</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AF32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG32" s="3">
         <v>100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-7200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-8100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E33" s="3">
         <v>400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-10900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>5400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3200</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF33" s="3">
+      <c r="AF33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-31500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-23200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-25500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-20500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>5500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,227 +3565,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E35" s="3">
         <v>400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-10900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>5400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3200</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF35" s="3">
+      <c r="AF35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-31500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-23200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-25500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-20500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>5500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42551</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3832,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,139 +3872,143 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E41" s="3">
         <v>50800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>55100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>70200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>59200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>60500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>66700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>107100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>123000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>207900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>222900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>254100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>275400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>286000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>301000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>40600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>15600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>11300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>15500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>24300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>8100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>24800</v>
       </c>
-      <c r="AC41" s="3">
-        <v>0</v>
-      </c>
       <c r="AD41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="3">
         <v>13400</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF41" s="3">
+      <c r="AF41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG41" s="3">
         <v>28600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>26600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>37300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>28800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>23700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>8</v>
+      <c r="D42" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>14700</v>
+      </c>
+      <c r="F42" s="3">
+        <v>14400</v>
       </c>
       <c r="G42" s="3">
-        <v>10100</v>
+        <v>13700</v>
       </c>
       <c r="H42" s="3">
         <v>10100</v>
       </c>
       <c r="I42" s="3">
+        <v>10100</v>
+      </c>
+      <c r="J42" s="3">
         <v>10000</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3931,8 +4021,8 @@
       <c r="N42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -4000,138 +4090,144 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>75800</v>
+        <v>78400</v>
       </c>
       <c r="E43" s="3">
+        <v>76500</v>
+      </c>
+      <c r="F43" s="3">
         <v>84200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>93800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>76500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>86400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>79100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>71500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>52700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>39400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>46700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>50400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>48300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>39600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>36000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>23800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>24700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>29500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>21000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>21300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>46600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>49300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>50700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>47300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>55900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>58900</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
-      </c>
       <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="3">
         <v>38500</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF43" s="3">
+      <c r="AF43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG43" s="3">
         <v>134000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>129700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>134100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>204000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>195900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>199000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4178,17 +4274,17 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA44" s="3">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB44" s="3">
         <v>200</v>
       </c>
-      <c r="AB44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC44" s="3" t="s">
-        <v>8</v>
+      <c r="AC44" s="3">
+        <v>0</v>
       </c>
       <c r="AD44" s="3" t="s">
         <v>8</v>
@@ -4196,240 +4292,249 @@
       <c r="AE44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AF44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG44" s="3">
         <v>92300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>153200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>144000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>185200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>165500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>181700</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>91200</v>
+        <v>82400</v>
       </c>
       <c r="E45" s="3">
-        <v>79700</v>
+        <v>75800</v>
       </c>
       <c r="F45" s="3">
-        <v>62500</v>
+        <v>65300</v>
       </c>
       <c r="G45" s="3">
-        <v>67800</v>
+        <v>48800</v>
       </c>
       <c r="H45" s="3">
-        <v>72200</v>
+        <v>44400</v>
       </c>
       <c r="I45" s="3">
-        <v>54900</v>
+        <v>33900</v>
       </c>
       <c r="J45" s="3">
+        <v>37300</v>
+      </c>
+      <c r="K45" s="3">
         <v>42100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>36000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>38400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>38800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>24700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>27500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>31500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>33200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>72300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>32300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>27600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>47700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>57400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>50800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>80900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>80500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>81200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>73800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>91600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>118100</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF45" s="3">
+      <c r="AF45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG45" s="3">
         <v>264300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>233600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>192100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>194500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>248100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>232700</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>211800</v>
+      </c>
+      <c r="E46" s="3">
         <v>217900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>218900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>226500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>213500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>229100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>210700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>220700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>211700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>285700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>308400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>329200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>351200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>357100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>370200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>136700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>72500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>68400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>84200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>103100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>106800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>138900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>138200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>135300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>138000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>175300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>170100</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF46" s="3">
+      <c r="AF46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG46" s="3">
         <v>519200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>543200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>507500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>612500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>633100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>652100</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4439,20 +4544,20 @@
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
-        <v>0</v>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3">
-        <v>10000</v>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>10000</v>
@@ -4463,8 +4568,8 @@
       <c r="M47" s="3">
         <v>10000</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
+      <c r="N47" s="3">
+        <v>10000</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
@@ -4481,8 +4586,8 @@
       <c r="S47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -4535,123 +4640,129 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>195700</v>
+      </c>
+      <c r="E48" s="3">
         <v>185200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>185900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>198400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>189100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>192800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>216500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>214800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>202700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>160600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>166300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>167100</v>
-      </c>
-      <c r="O48" s="3">
-        <v>167300</v>
       </c>
       <c r="P48" s="3">
         <v>167300</v>
       </c>
       <c r="Q48" s="3">
+        <v>167300</v>
+      </c>
+      <c r="R48" s="3">
         <v>166200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>168700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>186900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>183200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>187500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>192300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>211400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>249000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>226100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>190800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>192500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>195900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>154700</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF48" s="3">
+      <c r="AF48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG48" s="3">
         <v>537600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>486300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>491300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>547700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>568100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>603200</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>8</v>
+      <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
@@ -4660,7 +4771,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
         <v>1000</v>
@@ -4692,8 +4803,8 @@
       <c r="R49" s="3">
         <v>1000</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>8</v>
+      <c r="S49" s="3">
+        <v>1000</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>8</v>
@@ -4710,8 +4821,8 @@
       <c r="X49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
+      <c r="Y49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
@@ -4725,32 +4836,35 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>8</v>
+      <c r="AD49" s="3">
+        <v>0</v>
       </c>
       <c r="AE49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AF49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG49" s="3">
         <v>32200</v>
-      </c>
-      <c r="AG49" s="3">
-        <v>31900</v>
       </c>
       <c r="AH49" s="3">
         <v>31900</v>
       </c>
       <c r="AI49" s="3">
+        <v>31900</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>35500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>35800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>37200</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4970,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,115 +5080,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>36600</v>
+      </c>
+      <c r="F52" s="3">
+        <v>55300</v>
+      </c>
+      <c r="G52" s="3">
+        <v>50000</v>
+      </c>
+      <c r="H52" s="3">
+        <v>51800</v>
+      </c>
+      <c r="I52" s="3">
         <v>54700</v>
       </c>
-      <c r="E52" s="3">
-        <v>58700</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="J52" s="3">
         <v>53500</v>
       </c>
-      <c r="G52" s="3">
-        <v>51800</v>
-      </c>
-      <c r="H52" s="3">
-        <v>54700</v>
-      </c>
-      <c r="I52" s="3">
-        <v>53500</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>47200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>41800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>42900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>34200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>31900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>36400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>33800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>29700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>30400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>29700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>26500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>25300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>24600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>14500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>18400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>53400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>51700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>44900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>18500</v>
       </c>
-      <c r="AC52" s="3">
-        <v>0</v>
-      </c>
       <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="3">
         <v>11000</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF52" s="3">
+      <c r="AF52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG52" s="3">
         <v>66000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>65000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>57800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>50800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>51700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>46400</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5300,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>470100</v>
+      </c>
+      <c r="E54" s="3">
         <v>457800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>463500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>478400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>454400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>477700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>481700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>493900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>467200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>500300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>519900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>529300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>556000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>559200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>567100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>336900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>289100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>278000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>296900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>319900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>332700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>406300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>417700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>377700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>375400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>389600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>335700</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF54" s="3">
+      <c r="AF54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG54" s="3">
         <v>1154900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1126300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1088400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1246600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1288700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1338900</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5452,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,650 +5492,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>15200</v>
+        <v>15600</v>
       </c>
       <c r="E57" s="3">
-        <v>18500</v>
+        <v>17600</v>
       </c>
       <c r="F57" s="3">
-        <v>16200</v>
+        <v>24300</v>
       </c>
       <c r="G57" s="3">
-        <v>3100</v>
+        <v>21200</v>
       </c>
       <c r="H57" s="3">
-        <v>5400</v>
+        <v>5300</v>
       </c>
       <c r="I57" s="3">
-        <v>5900</v>
+        <v>7600</v>
       </c>
       <c r="J57" s="3">
+        <v>8100</v>
+      </c>
+      <c r="K57" s="3">
         <v>7100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>20400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>14000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>24600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>23700</v>
       </c>
-      <c r="AC57" s="3">
-        <v>0</v>
-      </c>
       <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="3">
         <v>25800</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF57" s="3">
+      <c r="AF57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG57" s="3">
         <v>203200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>221600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>223300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>281300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>280600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>302000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6400</v>
+        <v>6500</v>
       </c>
       <c r="E58" s="3">
-        <v>5500</v>
+        <v>7000</v>
       </c>
       <c r="F58" s="3">
-        <v>5900</v>
+        <v>6000</v>
       </c>
       <c r="G58" s="3">
-        <v>6000</v>
+        <v>6300</v>
       </c>
       <c r="H58" s="3">
-        <v>6700</v>
+        <v>7100</v>
       </c>
       <c r="I58" s="3">
-        <v>9900</v>
+        <v>7800</v>
       </c>
       <c r="J58" s="3">
+        <v>11100</v>
+      </c>
+      <c r="K58" s="3">
         <v>11000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>12300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>12800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>23000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>49100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>43500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>42100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>43900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>47800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>57100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>108900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>101900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>44500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>7100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>15100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>23700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>6600</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF58" s="3">
+      <c r="AF58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG58" s="3">
         <v>671400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>647600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>595400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>699000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>716500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>735600</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>29500</v>
+        <v>25700</v>
       </c>
       <c r="E59" s="3">
-        <v>33700</v>
+        <v>25400</v>
       </c>
       <c r="F59" s="3">
-        <v>34800</v>
+        <v>26400</v>
       </c>
       <c r="G59" s="3">
-        <v>30400</v>
+        <v>28500</v>
       </c>
       <c r="H59" s="3">
-        <v>29800</v>
+        <v>26600</v>
       </c>
       <c r="I59" s="3">
-        <v>27900</v>
+        <v>25700</v>
       </c>
       <c r="J59" s="3">
+        <v>23900</v>
+      </c>
+      <c r="K59" s="3">
         <v>25200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>20000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>19300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>19600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>23500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>32900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>19900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>27000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>38600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>41100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>42400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>43100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>56500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>77200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>61600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>73500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>112800</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AF59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG59" s="3">
         <v>150800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>101600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>85700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>82600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>89900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>91500</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E60" s="3">
         <v>51000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>57700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>57000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>39500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>41800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>43700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>43300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>34000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>31100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>33800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>35100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>36400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>36500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>51100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>88300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>73200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>75900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>89400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>109400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>113500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>162800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>170900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>133700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>93300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>104700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>145200</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF60" s="3">
+      <c r="AF60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG60" s="3">
         <v>1025400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>970800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>904400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1062900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1087000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1129100</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>35300</v>
+        <v>58200</v>
       </c>
       <c r="E61" s="3">
-        <v>33600</v>
+        <v>55700</v>
       </c>
       <c r="F61" s="3">
-        <v>33900</v>
+        <v>53600</v>
       </c>
       <c r="G61" s="3">
-        <v>33300</v>
+        <v>54500</v>
       </c>
       <c r="H61" s="3">
-        <v>35400</v>
+        <v>51000</v>
       </c>
       <c r="I61" s="3">
-        <v>37400</v>
+        <v>53500</v>
       </c>
       <c r="J61" s="3">
+        <v>57900</v>
+      </c>
+      <c r="K61" s="3">
         <v>37500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>38000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>21200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>26900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>30000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>31700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>36100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>38800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>44000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>48100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>44800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>52500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>50100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>68400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>81200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>89100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>119300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>153200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>157800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>32500</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>30300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>31100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>28800</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
       <c r="AK61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>23900</v>
-      </c>
-      <c r="E62" s="3">
-        <v>23600</v>
-      </c>
-      <c r="F62" s="3">
-        <v>24100</v>
-      </c>
-      <c r="G62" s="3">
-        <v>21000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>21600</v>
-      </c>
-      <c r="I62" s="3">
-        <v>24100</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" s="3">
         <v>24400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>15500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>15400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>19500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>19700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>20100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>21400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>20400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>21200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>22600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>22900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>21500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>33600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>35300</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AB62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
       </c>
       <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="3">
         <v>67500</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF62" s="3">
+      <c r="AF62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG62" s="3">
         <v>84400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>82600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>89000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>92000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>89500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>93600</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6260,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6370,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,115 +6480,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>148000</v>
+        <v>110700</v>
       </c>
       <c r="E66" s="3">
-        <v>152600</v>
+        <v>110200</v>
       </c>
       <c r="F66" s="3">
-        <v>153000</v>
+        <v>114800</v>
       </c>
       <c r="G66" s="3">
-        <v>132100</v>
+        <v>115000</v>
       </c>
       <c r="H66" s="3">
+        <v>93800</v>
+      </c>
+      <c r="I66" s="3">
+        <v>98900</v>
+      </c>
+      <c r="J66" s="3">
+        <v>105100</v>
+      </c>
+      <c r="K66" s="3">
+        <v>146600</v>
+      </c>
+      <c r="L66" s="3">
+        <v>128100</v>
+      </c>
+      <c r="M66" s="3">
+        <v>110100</v>
+      </c>
+      <c r="N66" s="3">
+        <v>120400</v>
+      </c>
+      <c r="O66" s="3">
+        <v>125300</v>
+      </c>
+      <c r="P66" s="3">
+        <v>133000</v>
+      </c>
+      <c r="Q66" s="3">
         <v>137200</v>
       </c>
-      <c r="I66" s="3">
-        <v>146000</v>
-      </c>
-      <c r="J66" s="3">
-        <v>146600</v>
-      </c>
-      <c r="K66" s="3">
-        <v>128100</v>
-      </c>
-      <c r="L66" s="3">
-        <v>110100</v>
-      </c>
-      <c r="M66" s="3">
-        <v>120400</v>
-      </c>
-      <c r="N66" s="3">
-        <v>125300</v>
-      </c>
-      <c r="O66" s="3">
-        <v>133000</v>
-      </c>
-      <c r="P66" s="3">
-        <v>137200</v>
-      </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>153800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>197800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>185700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>184400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>206600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>225200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>238300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>313900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>329600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>287000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>280700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>294400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>245200</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF66" s="3">
+      <c r="AF66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG66" s="3">
         <v>1141000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1084400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1022300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1154900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1176400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1224200</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6632,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6740,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6850,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +6960,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,115 +7070,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-441300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-446100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-446500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-440600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-438600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-429200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-437600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-437400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-431600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-434600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-434400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-432700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-431100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-431800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-438800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-439600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-441500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-443700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-446700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-442300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-431400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-433800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-438900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-433500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-428400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-429900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-435500</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG72" s="3">
         <v>-524700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-493200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-470000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-444500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-424000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-429500</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7290,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7400,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,115 +7510,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>319600</v>
+      </c>
+      <c r="E76" s="3">
         <v>309700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>311000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>325300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>322300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>340500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>335700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>347300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>339100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>390200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>399500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>404000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>422900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>422000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>413300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>139100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>103300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>93600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>90300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>94700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>94400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>92400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>88100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>90700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>94800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>95200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>90500</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF76" s="3">
+      <c r="AF76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG76" s="3">
         <v>13900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>41900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>66100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>91700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>112300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>114700</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +7730,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42551</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E81" s="3">
         <v>400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-10900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>5400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3200</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF81" s="3">
+      <c r="AF81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-31500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-23200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-25500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-20500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>5500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,34 +7997,35 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E83" s="3">
         <v>1500</v>
       </c>
-      <c r="E83" s="3">
-        <v>1800</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>8</v>
+      <c r="F83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G83" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H83" s="3">
+        <v>2000</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="J83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -7879,35 +8078,38 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD83" s="3">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE83" s="3">
         <v>4500</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF83" s="3">
+      <c r="AF83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG83" s="3">
         <v>17800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>20900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>24100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>19900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>18100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8215,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8325,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8435,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8545,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,68 +8655,71 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-23700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-10600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-14400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-10500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>5300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-9900</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>8</v>
       </c>
@@ -8518,38 +8735,41 @@
       <c r="AA89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD89" s="3">
+      <c r="AB89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE89" s="3">
         <v>18400</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AF89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-33800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>44600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-9100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,31 +8807,32 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3900</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-2800</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-10700</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-1500</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-2200</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8667,35 +8888,38 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD91" s="3">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-80300</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AF91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-11300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-11400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9025,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,68 +9135,71 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>6900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>10100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-31200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>26100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>1200</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>8</v>
       </c>
@@ -8985,38 +9215,41 @@
       <c r="AA94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD94" s="3">
+      <c r="AB94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-156400</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AF94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-30100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>17900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>26000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>5200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,31 +9287,32 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -9161,8 +9395,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9505,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9615,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,68 +9725,71 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-8200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-16200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-45700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-14200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-23700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>244800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>32600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>8300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-9400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1400</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>8</v>
       </c>
@@ -9559,205 +9805,211 @@
       <c r="AA100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD100" s="3">
+      <c r="AB100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE100" s="3">
         <v>102400</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AF100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG100" s="3">
         <v>16000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>50700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-48900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-4200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="F101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J101" s="3">
+        <v>800</v>
+      </c>
+      <c r="K101" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N101" s="3">
+        <v>800</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="P101" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="T101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="U101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="V101" s="3">
+        <v>1900</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>11600</v>
+      </c>
+      <c r="AF101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AH101" s="3">
         <v>2500</v>
       </c>
-      <c r="F101" s="3">
-        <v>400</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="I101" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M101" s="3">
-        <v>800</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="O101" s="3">
-        <v>100</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="U101" s="3">
-        <v>1900</v>
-      </c>
-      <c r="V101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>11600</v>
-      </c>
-      <c r="AE101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AG101" s="3">
-        <v>2500</v>
-      </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-6800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-15100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-40600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-15700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-85000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-14900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-31500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-21500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>260300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>24300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-8100</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>8</v>
       </c>
@@ -9773,34 +10025,37 @@
       <c r="AA102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AB102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-23900</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AF102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG102" s="3">
         <v>2000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-10700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>8500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>5100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-15000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
   <si>
     <t>SOL</t>
   </si>
@@ -656,493 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42551</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E8" s="3">
         <v>12900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>30100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>45000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>33800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>28900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>22800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>18500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>22800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>9700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>26200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>21200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>26500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>66000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>13600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>13100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>18800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>27800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>44800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>103000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>36300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>151600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>156600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>232100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>187000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>250000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>260700</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E9" s="3">
         <v>7200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>20700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>39900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>21200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>11300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>20300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>15600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>14400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>18800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>19800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>19400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>49700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>10200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>19600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>36400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>88800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>29900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>147500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>154900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>227100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>168200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>208900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>216200</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E10" s="3">
         <v>5600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>12700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>7200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>11300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>7400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>7100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>16300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>10500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>14200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>6400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>18800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>41100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>44500</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1181,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1273,26 +1286,29 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3">
         <v>5400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>5700</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>5400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>6300</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>7400</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1401,85 +1417,88 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1300</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>400</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>300</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>1000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>5500</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
@@ -1487,8 +1506,8 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
@@ -1496,50 +1515,53 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI14" s="3">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>-100</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E15" s="3">
         <v>1800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1621,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1658,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E17" s="3">
         <v>10700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>27100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>47500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>28800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>25900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>24300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>21600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>22300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>39800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>58600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>15200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>21900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>38900</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AG17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH17" s="3">
         <v>172000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>174400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>254000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>198800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>243700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>248200</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E18" s="3">
         <v>2100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-300</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-2600</v>
       </c>
       <c r="H18" s="3">
         <v>-2600</v>
       </c>
       <c r="I18" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="J18" s="3">
         <v>5000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-13300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>7400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>7100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>5700</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>5900</v>
       </c>
       <c r="AD18" s="3">
         <v>5900</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>8</v>
+      <c r="AE18" s="3">
+        <v>5900</v>
       </c>
       <c r="AF18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH18" s="3">
         <v>-20400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-17800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-21900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-11800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>6300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1918,169 +1950,173 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1100</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>7200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>8100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E21" s="3">
         <v>8500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-5600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>500</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3">
         <v>-700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4400</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2120,324 +2156,333 @@
       <c r="AF21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH21" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>9400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>5700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>32500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>37200</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3">
         <v>700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1700</v>
-      </c>
-      <c r="P22" s="3">
-        <v>1000</v>
       </c>
       <c r="Q22" s="3">
         <v>1000</v>
       </c>
       <c r="R22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S22" s="3">
         <v>1500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>3900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>8600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>9200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>7400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>8200</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>8500</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E23" s="3">
         <v>6300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-14300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-29100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-26900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-22100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-22400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>5900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>-200</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
       <c r="AC24" s="3">
         <v>0</v>
       </c>
@@ -2445,31 +2490,34 @@
         <v>0</v>
       </c>
       <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
         <v>300</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG24" s="3">
+      <c r="AG24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH24" s="3">
         <v>2400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-3600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-1900</v>
-      </c>
-      <c r="AK24" s="3">
-        <v>400</v>
       </c>
       <c r="AL24" s="3">
         <v>400</v>
       </c>
+      <c r="AM24" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2578,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E26" s="3">
         <v>5700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3500</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
       <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
         <v>-2000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-14500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>6500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-5600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3200</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG26" s="3">
+      <c r="AG26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH26" s="3">
         <v>-31500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-23200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-25500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-20500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>5500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E27" s="3">
         <v>4800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-10900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-5400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>5400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3200</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG27" s="3">
+      <c r="AG27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH27" s="3">
         <v>-31500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-23200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-25500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-20500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>5500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2908,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2976,17 +3036,17 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2994,8 +3054,8 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF29" s="3">
         <v>0</v>
@@ -3018,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3128,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3238,228 +3304,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E32" s="3">
         <v>4600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH32" s="3">
         <v>100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-7200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>2400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-8100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E33" s="3">
         <v>4800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-10900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-5400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>5400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3200</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG33" s="3">
+      <c r="AG33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH33" s="3">
         <v>-31500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-23200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-25500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-20500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>5500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3568,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E35" s="3">
         <v>4800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-10900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-5400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>5400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3200</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG35" s="3">
+      <c r="AG35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH35" s="3">
         <v>-31500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-23200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-25500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-20500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>5500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42551</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3833,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3873,145 +3958,149 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E41" s="3">
         <v>35800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>50800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>55100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>70200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>59200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>60500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>66700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>107100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>123000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>207900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>222900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>254100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>275400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>286000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>301000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>40600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>15600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>11300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>15500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>24300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>24800</v>
       </c>
-      <c r="AD41" s="3">
-        <v>0</v>
-      </c>
       <c r="AE41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="3">
         <v>13400</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG41" s="3">
+      <c r="AG41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH41" s="3">
         <v>28600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>26600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>37300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>28800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>23700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>15300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>14700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>14400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>13700</v>
-      </c>
-      <c r="H42" s="3">
-        <v>10100</v>
       </c>
       <c r="I42" s="3">
         <v>10100</v>
       </c>
       <c r="J42" s="3">
+        <v>10100</v>
+      </c>
+      <c r="K42" s="3">
         <v>10000</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>8</v>
       </c>
@@ -4024,8 +4113,8 @@
       <c r="O42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -4093,118 +4182,124 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>70500</v>
+      </c>
+      <c r="E43" s="3">
         <v>78400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>76500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>84200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>93800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>76500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>86400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>79100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>71500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>52700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>39400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>46700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>50400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>48300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>39600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>36000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>23800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>24700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>29500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>21000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>21300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>46600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>49300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>50700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>47300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>55900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>58900</v>
       </c>
-      <c r="AD43" s="3">
-        <v>0</v>
-      </c>
       <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="3">
         <v>38500</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG43" s="3">
+      <c r="AG43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH43" s="3">
         <v>134000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>129700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>134100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>204000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>195900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>199000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4229,8 +4324,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4277,17 +4372,17 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB44" s="3">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC44" s="3">
         <v>200</v>
       </c>
-      <c r="AC44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD44" s="3" t="s">
-        <v>8</v>
+      <c r="AD44" s="3">
+        <v>0</v>
       </c>
       <c r="AE44" s="3" t="s">
         <v>8</v>
@@ -4295,246 +4390,255 @@
       <c r="AF44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AG44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH44" s="3">
         <v>92300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>153200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>144000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>185200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>165500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>181700</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E45" s="3">
         <v>82400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>75800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>65300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>48800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>44400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>33900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>37300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>42100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>36000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>38400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>38800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>24700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>27500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>31500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>33200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>72300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>32300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>27600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>47700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>57400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>50800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>80900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>80500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>81200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>73800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>91600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>118100</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG45" s="3">
+      <c r="AG45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH45" s="3">
         <v>264300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>233600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>192100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>194500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>248100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>232700</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>191400</v>
+      </c>
+      <c r="E46" s="3">
         <v>211800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>217900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>218900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>226500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>213500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>229100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>210700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>220700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>211700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>285700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>308400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>329200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>351200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>357100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>370200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>136700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>72500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>68400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>84200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>103100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>106800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>138900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>138200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>135300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>138000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>175300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>170100</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG46" s="3">
+      <c r="AG46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH46" s="3">
         <v>519200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>543200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>507500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>612500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>633100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>652100</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4559,8 +4663,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>10000</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>10000</v>
@@ -4571,8 +4675,8 @@
       <c r="N47" s="3">
         <v>10000</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>8</v>
+      <c r="O47" s="3">
+        <v>10000</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>8</v>
@@ -4589,8 +4693,8 @@
       <c r="T47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -4643,118 +4747,124 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>219300</v>
+      </c>
+      <c r="E48" s="3">
         <v>195700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>185200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>185900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>198400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>189100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>192800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>216500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>214800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>202700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>160600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>166300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>167100</v>
-      </c>
-      <c r="P48" s="3">
-        <v>167300</v>
       </c>
       <c r="Q48" s="3">
         <v>167300</v>
       </c>
       <c r="R48" s="3">
+        <v>167300</v>
+      </c>
+      <c r="S48" s="3">
         <v>166200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>168700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>186900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>183200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>187500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>192300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>211400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>249000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>226100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>190800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>192500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>195900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>154700</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH48" s="3">
         <v>537600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>486300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>491300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>547700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>568100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>603200</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4774,7 +4884,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>1000</v>
@@ -4806,8 +4916,8 @@
       <c r="S49" s="3">
         <v>1000</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>8</v>
+      <c r="T49" s="3">
+        <v>1000</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>8</v>
@@ -4824,8 +4934,8 @@
       <c r="Y49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
+      <c r="Z49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA49" s="3">
         <v>0</v>
@@ -4839,32 +4949,35 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>8</v>
+      <c r="AE49" s="3">
+        <v>0</v>
       </c>
       <c r="AF49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AG49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH49" s="3">
         <v>32200</v>
-      </c>
-      <c r="AH49" s="3">
-        <v>31900</v>
       </c>
       <c r="AI49" s="3">
         <v>31900</v>
       </c>
       <c r="AJ49" s="3">
+        <v>31900</v>
+      </c>
+      <c r="AK49" s="3">
         <v>35500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>35800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>37200</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4973,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5083,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E52" s="3">
         <v>44400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>36600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>55300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>50000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>51800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>54700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>53500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>47200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>41800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>42900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>34200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>31900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>36400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>33800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>29700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>30400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>29700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>26500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>25300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>24600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>14500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>18400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>53400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>51700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>44900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>18500</v>
       </c>
-      <c r="AD52" s="3">
-        <v>0</v>
-      </c>
       <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3">
         <v>11000</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH52" s="3">
         <v>66000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>65000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>57800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>50800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>51700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>46400</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5303,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>447600</v>
+      </c>
+      <c r="E54" s="3">
         <v>470100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>457800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>463500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>478400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>454400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>477700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>481700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>493900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>467200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>500300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>519900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>529300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>556000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>559200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>567100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>336900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>289100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>278000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>296900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>319900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>332700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>406300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>417700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>377700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>375400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>389600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>335700</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG54" s="3">
+      <c r="AG54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH54" s="3">
         <v>1154900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1126300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1088400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1246600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1288700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1338900</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5453,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5493,558 +5622,574 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E57" s="3">
         <v>15600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>17600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>24300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>21200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>20400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>14000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>10800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>24600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>23700</v>
       </c>
-      <c r="AD57" s="3">
-        <v>0</v>
-      </c>
       <c r="AE57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="3">
         <v>25800</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH57" s="3">
         <v>203200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>221600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>223300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>281300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>280600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>302000</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E58" s="3">
         <v>6500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>12200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>12300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>12800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>23000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>49100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>43500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>42100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>43900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>47800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>57100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>108900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>101900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>44500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>7100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>15100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>23700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>6600</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG58" s="3">
+      <c r="AG58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH58" s="3">
         <v>671400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>647600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>595400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>699000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>716500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>735600</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E59" s="3">
         <v>25700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>25400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>26400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>28500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>26600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>25700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>23900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>25200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>20000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>19300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>19600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>23500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>32900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>19900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>27000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>38600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>41100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>42400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>43100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>56500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>77200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>61600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>73500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>112800</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH59" s="3">
         <v>150800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>101600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>85700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>82600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>89900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>91500</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>49500</v>
+      </c>
+      <c r="E60" s="3">
         <v>48800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>51000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>57700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>57000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>39500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>41800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>43700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>43300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>34000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>31100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>33800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>35100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>36400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>36500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>51100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>88300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>73200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>75900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>89400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>109400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>113500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>162800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>170900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>133700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>93300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>104700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>145200</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG60" s="3">
+      <c r="AG60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH60" s="3">
         <v>1025400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>970800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>904400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1062900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1087000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1129100</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>56500</v>
+      </c>
+      <c r="E61" s="3">
         <v>58200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>55700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>53600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>54500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>51000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>53500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>57900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>37500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>38000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>21200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>26900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>30000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>31700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>36100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>38800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>44000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>48100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>44800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>52500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>50100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>68400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>81200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>89100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>119300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>153200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>157800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>32500</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>30300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>31100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>28800</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
       <c r="AK61" s="3">
         <v>0</v>
       </c>
       <c r="AL61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM61" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6069,92 +6214,95 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3">
         <v>24400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>15500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>19500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>19700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>20100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>21400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>20400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>21200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>22600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>22900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>21500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>33600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>35300</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
+      <c r="AC62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD62" s="3">
         <v>0</v>
       </c>
       <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="3">
         <v>67500</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH62" s="3">
         <v>84400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>82600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>89000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>92000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>89500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>93600</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6263,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6373,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6483,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>109500</v>
+      </c>
+      <c r="E66" s="3">
         <v>110700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>110200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>114800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>115000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>93800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>98900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>105100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>146600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>128100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>110100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>120400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>125300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>133000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>137200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>153800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>197800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>185700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>184400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>206600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>225200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>238300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>313900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>329600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>287000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>280700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>294400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>245200</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG66" s="3">
+      <c r="AG66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH66" s="3">
         <v>1141000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1084400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1022300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1154900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1176400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1224200</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6633,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6743,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6853,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6963,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7073,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-453000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-441300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-446100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-446500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-440600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-438600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-429200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-437600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-437400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-431600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-434600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-434400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-432700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-431100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-431800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-438800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-439600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-441500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-443700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-446700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-442300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-431400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-433800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-438900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-433500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-428400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-429900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-435500</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH72" s="3">
         <v>-524700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-493200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-470000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-444500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-424000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-429500</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7293,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7403,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7513,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>300500</v>
+      </c>
+      <c r="E76" s="3">
         <v>319600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>309700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>311000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>325300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>322300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>340500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>335700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>347300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>339100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>390200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>399500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>404000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>422900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>422000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>413300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>139100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>103300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>93600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>90300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>94700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>94400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>92400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>88100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>90700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>94800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>95200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>90500</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG76" s="3">
+      <c r="AG76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH76" s="3">
         <v>13900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>41900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>66100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>91700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>112300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>114700</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7733,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42551</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E81" s="3">
         <v>4800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-10900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-5400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>5400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3200</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG81" s="3">
+      <c r="AG81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH81" s="3">
         <v>-31500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-23200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-25500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-20500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>5500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7998,37 +8195,38 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E83" s="3">
         <v>1900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2000</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" s="3">
         <v>1500</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -8081,35 +8279,38 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF83" s="3">
         <v>4500</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH83" s="3">
         <v>17800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>20900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>24100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>19900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>18100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8218,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8328,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8438,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8548,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8658,71 +8871,74 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-23700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-10600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-14400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>8800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-10500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-9900</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>8</v>
       </c>
@@ -8738,38 +8954,41 @@
       <c r="AB89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF89" s="3">
         <v>18400</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-33800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>44600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-9100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8808,35 +9027,36 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2000</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -8891,35 +9111,38 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-80300</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-11300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-11400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9028,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9138,71 +9364,74 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>6900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>10100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-31200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>26100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>1200</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>8</v>
       </c>
@@ -9218,38 +9447,41 @@
       <c r="AB94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-156400</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-30100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>17900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>26000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>5200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9288,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9314,8 +9547,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -9398,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9508,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9618,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9728,71 +9970,74 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-16200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-45700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-14200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-23700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-14300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>244800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>32600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>8300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-9400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1400</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>8</v>
       </c>
@@ -9808,101 +10053,104 @@
       <c r="AB100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AC100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF100" s="3">
         <v>102400</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH100" s="3">
         <v>16000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>50700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-48900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-4200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-5200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1900</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X101" s="3" t="s">
         <v>8</v>
       </c>
@@ -9918,101 +10166,104 @@
       <c r="AB101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE101" s="3">
+      <c r="AC101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF101" s="3">
         <v>11600</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG101" s="3">
+      <c r="AG101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>2500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>2400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-6800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-15100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-15100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>11000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-40600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-15700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-85000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-14900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-31500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-21500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-15000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>260300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>24300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-8100</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>8</v>
       </c>
@@ -10028,34 +10279,37 @@
       <c r="AB102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-23900</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH102" s="3">
         <v>2000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-10700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>8500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>5100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-15000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
   <si>
     <t>SOL</t>
   </si>
@@ -656,505 +656,518 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42551</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E8" s="3">
         <v>34600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>30100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>45000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>33800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>28900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>22800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>18500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>22800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>16400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>9700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>26200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>21200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>26500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>66000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>13600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>13100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>18800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>27800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>44800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>103000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>36300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>151600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>156600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>232100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>187000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>250000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>260700</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E9" s="3">
         <v>29800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>20700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>39900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>21200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>20300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>7200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>16000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>14400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>18800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>19800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>19400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>49700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>12700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>10200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>19600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>36400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>88800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>29900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>147500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>154900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>227100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>168200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>208900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>216200</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E10" s="3">
         <v>4800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>12700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>7200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>11300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>7400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>7100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>16300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>10500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>14200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>6400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>5000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>18800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>41100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>44500</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1194,8 +1207,9 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1289,26 +1303,29 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI12" s="3">
         <v>5400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>5700</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>5400</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>6300</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>7400</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1420,8 +1437,11 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1429,79 +1449,79 @@
         <v>8</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>900</v>
       </c>
-      <c r="H14" s="3">
-        <v>4200</v>
-      </c>
       <c r="I14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J14" s="3">
         <v>1300</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>400</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>1000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>5500</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
@@ -1509,8 +1529,8 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
@@ -1518,53 +1538,56 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ14" s="3">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK14" s="3">
         <v>4700</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-100</v>
       </c>
-      <c r="AL14" s="3">
-        <v>0</v>
-      </c>
       <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E15" s="3">
         <v>1900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1800</v>
       </c>
-      <c r="H15" s="3">
-        <v>2000</v>
-      </c>
       <c r="I15" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J15" s="3">
         <v>1900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2100</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1646,8 +1669,11 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,234 +1710,241 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>36500</v>
+      </c>
+      <c r="F17" s="3">
+        <v>10700</v>
+      </c>
+      <c r="G17" s="3">
+        <v>27100</v>
+      </c>
+      <c r="H17" s="3">
+        <v>14900</v>
+      </c>
+      <c r="I17" s="3">
+        <v>49700</v>
+      </c>
+      <c r="J17" s="3">
+        <v>16600</v>
+      </c>
+      <c r="K17" s="3">
+        <v>28800</v>
+      </c>
+      <c r="L17" s="3">
+        <v>15900</v>
+      </c>
+      <c r="M17" s="3">
+        <v>25900</v>
+      </c>
+      <c r="N17" s="3">
+        <v>23800</v>
+      </c>
+      <c r="O17" s="3">
+        <v>8400</v>
+      </c>
+      <c r="P17" s="3">
+        <v>5700</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>24300</v>
+      </c>
+      <c r="R17" s="3">
+        <v>12800</v>
+      </c>
+      <c r="S17" s="3">
+        <v>11200</v>
+      </c>
+      <c r="T17" s="3">
+        <v>18700</v>
+      </c>
+      <c r="U17" s="3">
+        <v>15900</v>
+      </c>
+      <c r="V17" s="3">
+        <v>6900</v>
+      </c>
+      <c r="W17" s="3">
+        <v>21600</v>
+      </c>
+      <c r="X17" s="3">
+        <v>22300</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>39800</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>58600</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>6500</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>15200</v>
+      </c>
+      <c r="AC17" s="3">
+        <v>7500</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>13100</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>21900</v>
+      </c>
+      <c r="AF17" s="3">
         <v>38900</v>
       </c>
-      <c r="E17" s="3">
-        <v>10700</v>
-      </c>
-      <c r="F17" s="3">
-        <v>27100</v>
-      </c>
-      <c r="G17" s="3">
-        <v>14900</v>
-      </c>
-      <c r="H17" s="3">
-        <v>47500</v>
-      </c>
-      <c r="I17" s="3">
-        <v>16600</v>
-      </c>
-      <c r="J17" s="3">
-        <v>28800</v>
-      </c>
-      <c r="K17" s="3">
-        <v>15900</v>
-      </c>
-      <c r="L17" s="3">
-        <v>25900</v>
-      </c>
-      <c r="M17" s="3">
-        <v>23800</v>
-      </c>
-      <c r="N17" s="3">
-        <v>8400</v>
-      </c>
-      <c r="O17" s="3">
-        <v>5700</v>
-      </c>
-      <c r="P17" s="3">
-        <v>24300</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>12800</v>
-      </c>
-      <c r="R17" s="3">
-        <v>11200</v>
-      </c>
-      <c r="S17" s="3">
-        <v>18700</v>
-      </c>
-      <c r="T17" s="3">
-        <v>15900</v>
-      </c>
-      <c r="U17" s="3">
-        <v>6900</v>
-      </c>
-      <c r="V17" s="3">
-        <v>21600</v>
-      </c>
-      <c r="W17" s="3">
-        <v>22300</v>
-      </c>
-      <c r="X17" s="3">
-        <v>39800</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>58600</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>6500</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>15200</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>7500</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>13100</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>21900</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>38900</v>
-      </c>
-      <c r="AF17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AH17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI17" s="3">
         <v>172000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>174400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>254000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>198800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>243700</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>248200</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-4400</v>
+        <v>-4100</v>
       </c>
       <c r="E18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F18" s="3">
         <v>2100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="J18" s="3">
         <v>-2600</v>
       </c>
-      <c r="I18" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-13300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>7400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>7100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>5700</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>5900</v>
       </c>
       <c r="AE18" s="3">
         <v>5900</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>8</v>
+      <c r="AF18" s="3">
+        <v>5900</v>
       </c>
       <c r="AG18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AH18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI18" s="3">
         <v>-20400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-17800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-21900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-11800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>6300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1951,175 +1984,179 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E20" s="3">
         <v>9000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1100</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AH20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>7200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>8100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-11500</v>
+        <v>4200</v>
       </c>
       <c r="E21" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F21" s="3">
         <v>8500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1800</v>
       </c>
-      <c r="H21" s="3">
-        <v>5300</v>
-      </c>
       <c r="I21" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J21" s="3">
         <v>-5600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>500</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>8400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4400</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2159,333 +2196,342 @@
       <c r="AG21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI21" s="3">
         <v>-2600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>9400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>5700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>32500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>37200</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>400</v>
+      </c>
+      <c r="E22" s="3">
+        <v>400</v>
+      </c>
+      <c r="F22" s="3">
+        <v>700</v>
+      </c>
+      <c r="G22" s="3">
+        <v>500</v>
+      </c>
+      <c r="H22" s="3">
+        <v>400</v>
+      </c>
+      <c r="I22" s="3">
+        <v>800</v>
+      </c>
+      <c r="J22" s="3">
+        <v>500</v>
+      </c>
+      <c r="K22" s="3">
         <v>200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="L22" s="3">
         <v>700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="M22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
-        <v>400</v>
-      </c>
-      <c r="H22" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I22" s="3">
-        <v>500</v>
-      </c>
-      <c r="J22" s="3">
-        <v>200</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="N22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O22" s="3">
+        <v>800</v>
+      </c>
+      <c r="P22" s="3">
         <v>700</v>
       </c>
-      <c r="L22" s="3">
-        <v>500</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1100</v>
-      </c>
-      <c r="N22" s="3">
-        <v>800</v>
-      </c>
-      <c r="O22" s="3">
-        <v>700</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1700</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>1000</v>
       </c>
       <c r="R22" s="3">
         <v>1000</v>
       </c>
       <c r="S22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T22" s="3">
         <v>1500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>3900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>8600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>9200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>7400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>8200</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>8500</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-13700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-14300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-5500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-29100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-26900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-22100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-22400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>5900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>700</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>-200</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
         <v>0</v>
       </c>
@@ -2493,31 +2539,34 @@
         <v>0</v>
       </c>
       <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
         <v>300</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH24" s="3">
+      <c r="AH24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI24" s="3">
         <v>2400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-3600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>3400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-1900</v>
-      </c>
-      <c r="AL24" s="3">
-        <v>400</v>
       </c>
       <c r="AM24" s="3">
         <v>400</v>
       </c>
+      <c r="AN24" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2629,234 +2678,243 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3500</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
       <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
         <v>-2000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-14500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>6500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-5600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>5400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3200</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH26" s="3">
+      <c r="AH26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI26" s="3">
         <v>-31500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-23200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-25500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-20500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>5500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-11800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-10900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>5100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-5400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>5400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3200</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH27" s="3">
+      <c r="AH27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI27" s="3">
         <v>-31500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-23200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-25500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-20500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>5500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2968,8 +3026,11 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3039,17 +3100,17 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -3057,8 +3118,8 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG29" s="3">
         <v>0</v>
@@ -3081,8 +3142,11 @@
       <c r="AM29" s="3">
         <v>0</v>
       </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3194,8 +3258,11 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3307,234 +3374,243 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-9000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AH32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI32" s="3">
         <v>100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-7200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>2400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-8100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-11800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-10900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>5100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-5400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>5400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3200</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH33" s="3">
+      <c r="AH33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI33" s="3">
         <v>-31500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-23200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-25500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-20500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>5500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3646,239 +3722,248 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-11800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-10900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>5100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-5400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>5400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3200</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH35" s="3">
+      <c r="AH35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI35" s="3">
         <v>-31500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-23200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-25500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-20500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>5500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42551</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3918,8 +4003,9 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3959,121 +4045,125 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>52900</v>
+      </c>
+      <c r="E41" s="3">
         <v>50000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>35800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>50800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>55100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>70200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>59200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>60500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>66700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>107100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>123000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>207900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>222900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>254100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>275400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>286000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>301000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>40600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>15600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>11300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>15500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>24300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>8100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>24800</v>
       </c>
-      <c r="AE41" s="3">
-        <v>0</v>
-      </c>
       <c r="AF41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="3">
         <v>13400</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH41" s="3">
+      <c r="AH41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI41" s="3">
         <v>28600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>26600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>37300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>28800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>23700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4081,29 +4171,29 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>9900</v>
+      </c>
+      <c r="F42" s="3">
         <v>15300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>14700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>14400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>13700</v>
-      </c>
-      <c r="I42" s="3">
-        <v>10100</v>
       </c>
       <c r="J42" s="3">
         <v>10100</v>
       </c>
       <c r="K42" s="3">
+        <v>10100</v>
+      </c>
+      <c r="L42" s="3">
         <v>10000</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>8</v>
       </c>
@@ -4116,8 +4206,8 @@
       <c r="P42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -4185,121 +4275,127 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>70500</v>
+        <v>73700</v>
       </c>
       <c r="E43" s="3">
+        <v>70800</v>
+      </c>
+      <c r="F43" s="3">
         <v>78400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>76500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>84200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>93800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>76500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>86400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>79100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>71500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>52700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>39400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>46700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>50400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>48300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>39600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>36000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>23800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>24700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>29500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>21000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>21300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>46600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>49300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>50700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>47300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>55900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>58900</v>
       </c>
-      <c r="AE43" s="3">
-        <v>0</v>
-      </c>
       <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="3">
         <v>38500</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH43" s="3">
+      <c r="AH43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI43" s="3">
         <v>134000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>129700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>134100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>204000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>195900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>199000</v>
       </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4327,8 +4423,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4375,17 +4471,17 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC44" s="3">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD44" s="3">
         <v>200</v>
       </c>
-      <c r="AD44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE44" s="3" t="s">
-        <v>8</v>
+      <c r="AE44" s="3">
+        <v>0</v>
       </c>
       <c r="AF44" s="3" t="s">
         <v>8</v>
@@ -4393,252 +4489,261 @@
       <c r="AG44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AH44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI44" s="3">
         <v>92300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>153200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>144000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>185200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>165500</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>181700</v>
       </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>54800</v>
+        <v>51500</v>
       </c>
       <c r="E45" s="3">
+        <v>60700</v>
+      </c>
+      <c r="F45" s="3">
         <v>82400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>75800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>65300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>48800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>44400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>33900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>37300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>42100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>36000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>38400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>38800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>24700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>27500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>31500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>33200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>72300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>32300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>27600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>47700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>57400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>50800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>80900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>80500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>81200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>73800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>91600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>118100</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH45" s="3">
+      <c r="AH45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI45" s="3">
         <v>264300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>233600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>192100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>194500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>248100</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>232700</v>
       </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>197100</v>
+      </c>
+      <c r="E46" s="3">
         <v>191400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>211800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>217900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>218900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>226500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>213500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>229100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>210700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>220700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>211700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>285700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>308400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>329200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>351200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>357100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>370200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>136700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>72500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>68400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>84200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>103100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>106800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>138900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>138200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>135300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>138000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>175300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>170100</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH46" s="3">
+      <c r="AH46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI46" s="3">
         <v>519200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>543200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>507500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>612500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>633100</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>652100</v>
       </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4666,8 +4771,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>10000</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>10000</v>
@@ -4678,8 +4783,8 @@
       <c r="O47" s="3">
         <v>10000</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>8</v>
+      <c r="P47" s="3">
+        <v>10000</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>8</v>
@@ -4696,8 +4801,8 @@
       <c r="U47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -4750,121 +4855,127 @@
       <c r="AM47" s="3">
         <v>0</v>
       </c>
+      <c r="AN47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>221400</v>
+      </c>
+      <c r="E48" s="3">
         <v>219300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>195700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>185200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>185900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>198400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>189100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>192800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>216500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>214800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>202700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>160600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>166300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>167100</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>167300</v>
       </c>
       <c r="R48" s="3">
         <v>167300</v>
       </c>
       <c r="S48" s="3">
+        <v>167300</v>
+      </c>
+      <c r="T48" s="3">
         <v>166200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>168700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>186900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>183200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>187500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>192300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>211400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>249000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>226100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>190800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>192500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>195900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>154700</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH48" s="3">
+      <c r="AH48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI48" s="3">
         <v>537600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>486300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>491300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>547700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>568100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>603200</v>
       </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4887,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="K49" s="3">
         <v>1000</v>
@@ -4919,8 +5030,8 @@
       <c r="T49" s="3">
         <v>1000</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>8</v>
+      <c r="U49" s="3">
+        <v>1000</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>8</v>
@@ -4937,8 +5048,8 @@
       <c r="Z49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA49" s="3">
-        <v>0</v>
+      <c r="AA49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB49" s="3">
         <v>0</v>
@@ -4952,32 +5063,35 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>8</v>
+      <c r="AF49" s="3">
+        <v>0</v>
       </c>
       <c r="AG49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AH49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI49" s="3">
         <v>32200</v>
-      </c>
-      <c r="AI49" s="3">
-        <v>31900</v>
       </c>
       <c r="AJ49" s="3">
         <v>31900</v>
       </c>
       <c r="AK49" s="3">
+        <v>31900</v>
+      </c>
+      <c r="AL49" s="3">
         <v>35500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>35800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>37200</v>
       </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5089,8 +5203,11 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5202,121 +5319,127 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>36800</v>
+        <v>46500</v>
       </c>
       <c r="E52" s="3">
+        <v>19600</v>
+      </c>
+      <c r="F52" s="3">
         <v>44400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>36600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>55300</v>
       </c>
-      <c r="H52" s="3">
-        <v>50000</v>
-      </c>
       <c r="I52" s="3">
+        <v>37100</v>
+      </c>
+      <c r="J52" s="3">
         <v>51800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>54700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>53500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>47200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>41800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>42900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>34200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>31900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>36400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>33800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>29700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>30400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>29700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>26500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>25300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>24600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>14500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>18400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>53400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>51700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>44900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>18500</v>
       </c>
-      <c r="AE52" s="3">
-        <v>0</v>
-      </c>
       <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
         <v>11000</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH52" s="3">
+      <c r="AH52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI52" s="3">
         <v>66000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>65000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>57800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>50800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>51700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>46400</v>
       </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5428,121 +5551,127 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>464900</v>
+      </c>
+      <c r="E54" s="3">
         <v>447600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>470100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>457800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>463500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>478400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>454400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>477700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>481700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>493900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>467200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>500300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>519900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>529300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>556000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>559200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>567100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>336900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>289100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>278000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>296900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>319900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>332700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>406300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>417700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>377700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>375400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>389600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>335700</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH54" s="3">
+      <c r="AH54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI54" s="3">
         <v>1154900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1126300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1088400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1246600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1288700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1338900</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5582,8 +5711,9 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5623,573 +5753,589 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E57" s="3">
         <v>15900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>24300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>21200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>20400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>14000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>10800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>24600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>23700</v>
       </c>
-      <c r="AE57" s="3">
-        <v>0</v>
-      </c>
       <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="3">
         <v>25800</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH57" s="3">
+      <c r="AH57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI57" s="3">
         <v>203200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>221600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>223300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>281300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>280600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>302000</v>
       </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E58" s="3">
         <v>6900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>12200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>11400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>12300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>12800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>23000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>49100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>43500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>42100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>43900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>47800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>57100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>108900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>101900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>44500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>15100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>23700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>6600</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH58" s="3">
+      <c r="AH58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI58" s="3">
         <v>671400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>647600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>595400</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>699000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>716500</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>735600</v>
       </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>25500</v>
+        <v>25100</v>
       </c>
       <c r="E59" s="3">
+        <v>25200</v>
+      </c>
+      <c r="F59" s="3">
         <v>25700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>25400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>26400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>28500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>26600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>25700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>23900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>25200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>20000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>19300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>19600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>23500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>32900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>19900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>27000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>38600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>41100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>42400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>43100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>56500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>77200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>61600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>73500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>112800</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH59" s="3">
+      <c r="AH59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI59" s="3">
         <v>150800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>101600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>85700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>82600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>89900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>91500</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E60" s="3">
         <v>49500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>48800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>51000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>57700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>57000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>39500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>41800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>43700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>43300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>34000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>31100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>33800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>35100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>36400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>36500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>51100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>88300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>73200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>75900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>89400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>109400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>113500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>162800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>170900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>133700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>93300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>104700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>145200</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH60" s="3">
+      <c r="AH60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI60" s="3">
         <v>1025400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>970800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>904400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1062900</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1087000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1129100</v>
       </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>70700</v>
+      </c>
+      <c r="E61" s="3">
         <v>56500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>58200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>55700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>53600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>54500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>51000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>53500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>57900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>37500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>38000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>21200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>26900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>30000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>31700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>36100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>38800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>44000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>48100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>44800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>52500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>50100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>68400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>81200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>89100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>119300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>153200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>157800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>32500</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
       <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
         <v>30300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>31100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>28800</v>
       </c>
-      <c r="AK61" s="3">
-        <v>0</v>
-      </c>
       <c r="AL61" s="3">
         <v>0</v>
       </c>
       <c r="AM61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN61" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6217,92 +6363,95 @@
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3">
         <v>24400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>15800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>19500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>19700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>20100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>21400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>20400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>21200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>22600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>22900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>21500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>33600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>35300</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD62" s="3">
-        <v>0</v>
+      <c r="AD62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE62" s="3">
         <v>0</v>
       </c>
       <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="3">
         <v>67500</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH62" s="3">
+      <c r="AH62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI62" s="3">
         <v>84400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>82600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>89000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>92000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>89500</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>93600</v>
       </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6414,8 +6563,11 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6527,8 +6679,11 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6640,121 +6795,127 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>123300</v>
+      </c>
+      <c r="E66" s="3">
         <v>109500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>110700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>110200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>114800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>115000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>93800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>98900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>105100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>146600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>128100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>110100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>120400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>125300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>133000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>137200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>153800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>197800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>185700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>184400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>206600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>225200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>238300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>313900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>329600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>287000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>280700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>294400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>245200</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH66" s="3">
+      <c r="AH66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI66" s="3">
         <v>1141000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1084400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1022300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1154900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1176400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1224200</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6794,8 +6955,9 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6907,8 +7069,11 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7020,8 +7185,11 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7133,8 +7301,11 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7246,121 +7417,127 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-451500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-453000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-441300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-446100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-446500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-440600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-438600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-429200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-437600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-437400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-431600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-434600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-434400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-432700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-431100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-431800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-438800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-439600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-441500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-443700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-446700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-442300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-431400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-433800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-438900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-433500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-428400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-429900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-435500</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH72" s="3">
+      <c r="AH72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI72" s="3">
         <v>-524700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-493200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-470000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-444500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-424000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-429500</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7472,8 +7649,11 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7585,8 +7765,11 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7698,121 +7881,127 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>304100</v>
+      </c>
+      <c r="E76" s="3">
         <v>300500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>319600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>309700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>311000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>325300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>322300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>340500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>335700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>347300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>339100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>390200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>399500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>404000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>422900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>422000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>413300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>139100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>103300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>93600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>90300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>94700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>94400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>92400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>88100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>90700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>94800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>95200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>90500</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH76" s="3">
+      <c r="AH76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI76" s="3">
         <v>13900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>41900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>66100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>91700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>112300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>114700</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7924,239 +8113,248 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42551</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-11800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-10900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>5100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-5400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>5400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3200</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH81" s="3">
+      <c r="AH81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI81" s="3">
         <v>-31500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-23200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-25500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-20500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>5500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8196,40 +8394,41 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4400</v>
+        <v>1800</v>
       </c>
       <c r="E83" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F83" s="3">
         <v>1900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2000</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L83" s="3">
         <v>1500</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -8282,35 +8481,38 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF83" s="3">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG83" s="3">
         <v>4500</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH83" s="3">
+      <c r="AH83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI83" s="3">
         <v>17800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>20900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>24100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>19900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>18100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8422,8 +8624,11 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8535,8 +8740,11 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8648,8 +8856,11 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8761,8 +8972,11 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8874,74 +9088,77 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>10400</v>
+        <v>-1900</v>
       </c>
       <c r="E89" s="3">
+        <v>10300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-5600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-23700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-10600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-14400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>8800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-10500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>5300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-9900</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>8</v>
       </c>
@@ -8957,38 +9174,41 @@
       <c r="AC89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AD89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG89" s="3">
         <v>18400</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH89" s="3">
+      <c r="AH89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-33800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>44600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-9100</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9028,38 +9248,39 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>8</v>
+      <c r="D91" s="3">
+        <v>-2700</v>
       </c>
       <c r="E91" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-4200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2800</v>
       </c>
-      <c r="H91" s="3">
-        <v>-10700</v>
-      </c>
       <c r="I91" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="J91" s="3">
         <v>-1500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2000</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -9114,35 +9335,38 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-80300</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH91" s="3">
+      <c r="AH91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-11300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-11400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9254,8 +9478,11 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9367,74 +9594,77 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-5000</v>
+        <v>-2100</v>
       </c>
       <c r="E94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-4200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>6900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>10100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-31200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>26100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1200</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>8</v>
       </c>
@@ -9450,38 +9680,41 @@
       <c r="AC94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AD94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-156400</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH94" s="3">
+      <c r="AH94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-30100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>17900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>26000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>5200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9521,8 +9754,9 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9550,8 +9784,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9634,8 +9868,11 @@
       <c r="AM96" s="3">
         <v>0</v>
       </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9747,8 +9984,11 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9860,8 +10100,11 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9973,74 +10216,77 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>2800</v>
+        <v>13200</v>
       </c>
       <c r="E100" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-6700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-16200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-45700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-14200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-23700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-14300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>244800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>32600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>8300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-9400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1400</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>8</v>
       </c>
@@ -10056,104 +10302,107 @@
       <c r="AC100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AD100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG100" s="3">
         <v>102400</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH100" s="3">
+      <c r="AH100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI100" s="3">
         <v>16000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>50700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-48900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-4200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E101" s="3">
         <v>400</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-5200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1900</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y101" s="3" t="s">
         <v>8</v>
       </c>
@@ -10169,104 +10418,107 @@
       <c r="AC101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF101" s="3">
+      <c r="AD101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG101" s="3">
         <v>11600</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH101" s="3">
+      <c r="AH101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>2400</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-6800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E102" s="3">
         <v>14300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-15100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-15100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>11000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-40600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-85000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-14900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-31500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-21500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-15000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>260300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>24300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-8100</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>8</v>
       </c>
@@ -10282,34 +10534,37 @@
       <c r="AC102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AD102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG102" s="3">
         <v>-23900</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH102" s="3">
+      <c r="AH102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI102" s="3">
         <v>2000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-10700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>8500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>5100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-15000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
   <si>
     <t>SOL</t>
   </si>
@@ -656,518 +656,531 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42551</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E8" s="3">
         <v>8200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>34600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>12900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>30100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>45000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>33800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>28900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>22800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>15500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>18500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>22800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>16400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>9700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>26200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>21200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>26500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>66000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>13600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>13100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>18800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>27800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>44800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>103000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>36300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>151600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>156600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>232100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>187000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>250000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>260700</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E9" s="3">
         <v>4900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>29800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>20700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>39900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>21200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>11300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>20300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>15600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>7200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>16000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>18800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>19800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>19400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>49700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>12700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>10200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>19600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>36400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>88800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>29900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>147500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>154900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>227100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>168200</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>208900</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>216200</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E10" s="3">
         <v>3200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>9400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>12700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>7200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>11300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>6800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>7400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>7100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>16300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>10500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>14200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>6400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>4100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>5000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>18800</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>41100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>44500</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,8 +1221,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1306,26 +1320,29 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ12" s="3">
         <v>5400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>5700</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>5400</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>6300</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>7400</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,91 +1457,94 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>27300</v>
       </c>
       <c r="E14" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F14" s="3">
         <v>2500</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1300</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>400</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>1000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>5500</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
@@ -1532,8 +1552,8 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1541,56 +1561,59 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
-      <c r="AJ14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK14" s="3">
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL14" s="3">
         <v>4700</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>-100</v>
       </c>
-      <c r="AM14" s="3">
-        <v>0</v>
-      </c>
       <c r="AN14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E15" s="3">
         <v>2100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2100</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1672,8 +1695,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1737,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>12300</v>
+        <v>19400</v>
       </c>
       <c r="E17" s="3">
+        <v>9500</v>
+      </c>
+      <c r="F17" s="3">
         <v>36500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>27100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>49700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>28800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>25900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>23800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>24300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>21600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>22300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>39800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>58600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>15200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>13100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>21900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>38900</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AI17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ17" s="3">
         <v>172000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>174400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>254000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>198800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>243700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>248200</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-4100</v>
+        <v>-6500</v>
       </c>
       <c r="E18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-13300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>7400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>7100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>5700</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>5900</v>
       </c>
       <c r="AF18" s="3">
         <v>5900</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>8</v>
+      <c r="AG18" s="3">
+        <v>5900</v>
       </c>
       <c r="AH18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AI18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>-20400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-17800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-21900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-11800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>6300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,181 +2018,185 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>9000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1100</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AI20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>7200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>8100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4200</v>
+        <v>4300</v>
       </c>
       <c r="E21" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-9100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-5600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>500</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3">
         <v>-700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4400</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2199,342 +2236,351 @@
       <c r="AH21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>3300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>9400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>5700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>32500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>37200</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="E22" s="3">
         <v>400</v>
       </c>
       <c r="F22" s="3">
+        <v>400</v>
+      </c>
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1700</v>
-      </c>
-      <c r="R22" s="3">
-        <v>1000</v>
       </c>
       <c r="S22" s="3">
         <v>1000</v>
       </c>
       <c r="T22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U22" s="3">
         <v>1500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>3900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>8600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>9200</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>7400</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>8200</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>8500</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-25700</v>
+      </c>
+      <c r="E23" s="3">
         <v>2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-13700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-14300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-5500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>4000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-29100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-26900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-22100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-22400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>5900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E24" s="3">
         <v>700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>400</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
       <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>-200</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
       <c r="AE24" s="3">
         <v>0</v>
       </c>
@@ -2542,31 +2588,34 @@
         <v>0</v>
       </c>
       <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
         <v>300</v>
       </c>
-      <c r="AH24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI24" s="3">
+      <c r="AI24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-3600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>3400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-1900</v>
-      </c>
-      <c r="AM24" s="3">
-        <v>400</v>
       </c>
       <c r="AN24" s="3">
         <v>400</v>
       </c>
+      <c r="AO24" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,124 +2730,130 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="E26" s="3">
         <v>1500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3500</v>
       </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
       <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>7600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-14500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-5600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>5400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3200</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI26" s="3">
+      <c r="AI26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>-31500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-23200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-25500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-20500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>5500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2806,115 +2861,118 @@
         <v>1500</v>
       </c>
       <c r="E27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-11800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>7000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-10900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>5400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3200</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI27" s="3">
+      <c r="AI27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>-31500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-23200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-25500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-20500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>5500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3087,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3103,17 +3164,17 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -3121,8 +3182,8 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH29" s="3">
         <v>0</v>
@@ -3145,8 +3206,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3325,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,124 +3444,130 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E32" s="3">
         <v>6200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-9000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AI32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-7200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>2400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-8100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3502,115 +3575,118 @@
         <v>1500</v>
       </c>
       <c r="E33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-11800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>7000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-10900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>5400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3200</v>
       </c>
-      <c r="AH33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI33" s="3">
+      <c r="AI33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>-31500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-23200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-25500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-20500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>5500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,8 +3801,11 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3734,236 +3813,242 @@
         <v>1500</v>
       </c>
       <c r="E35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-11800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>7000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-10900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>5400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3200</v>
       </c>
-      <c r="AH35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI35" s="3">
+      <c r="AI35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>-31500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-23200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-25500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-20500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>5500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42551</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4089,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,157 +4132,161 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>46600</v>
+      </c>
+      <c r="E41" s="3">
         <v>52900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>50000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>35800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>50800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>55100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>70200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>59200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>60500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>66700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>107100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>123000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>207900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>222900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>254100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>275400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>286000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>301000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>40600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>15600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>11300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>15500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>24300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>8700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>8100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>24800</v>
       </c>
-      <c r="AF41" s="3">
-        <v>0</v>
-      </c>
       <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="3">
         <v>13400</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI41" s="3">
+      <c r="AI41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>28600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>26600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>37300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>28800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>23700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>12100</v>
       </c>
       <c r="E42" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F42" s="3">
         <v>9900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>15300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>14700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>14400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>13700</v>
-      </c>
-      <c r="J42" s="3">
-        <v>10100</v>
       </c>
       <c r="K42" s="3">
         <v>10100</v>
       </c>
       <c r="L42" s="3">
+        <v>10100</v>
+      </c>
+      <c r="M42" s="3">
         <v>10000</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>8</v>
       </c>
@@ -4209,8 +4299,8 @@
       <c r="Q42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -4278,124 +4368,130 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>73700</v>
+        <v>73600</v>
       </c>
       <c r="E43" s="3">
+        <v>73500</v>
+      </c>
+      <c r="F43" s="3">
         <v>70800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>78400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>76500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>84200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>93800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>76500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>86400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>79100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>71500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>52700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>39400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>46700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>50400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>48300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>39600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>36000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>23800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>24700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>29500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>21000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>21300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>46600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>49300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>50700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>47300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>55900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>58900</v>
       </c>
-      <c r="AF43" s="3">
-        <v>0</v>
-      </c>
       <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3">
         <v>38500</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI43" s="3">
+      <c r="AI43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ43" s="3">
         <v>134000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>129700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>134100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>204000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>195900</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>199000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4426,8 +4522,8 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4474,17 +4570,17 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD44" s="3">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE44" s="3">
         <v>200</v>
       </c>
-      <c r="AE44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF44" s="3" t="s">
-        <v>8</v>
+      <c r="AF44" s="3">
+        <v>0</v>
       </c>
       <c r="AG44" s="3" t="s">
         <v>8</v>
@@ -4492,258 +4588,267 @@
       <c r="AH44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AI44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ44" s="3">
         <v>92300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>153200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>144000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>185200</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>165500</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>181700</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>51500</v>
+        <v>53400</v>
       </c>
       <c r="E45" s="3">
+        <v>58700</v>
+      </c>
+      <c r="F45" s="3">
         <v>60700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>82400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>75800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>65300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>48800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>44400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>33900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>37300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>42100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>36000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>38400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>38800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>24700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>27500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>31500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>33200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>72300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>32300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>27600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>47700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>57400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>50800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>80900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>80500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>81200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>73800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>91600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>118100</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI45" s="3">
+      <c r="AI45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>264300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>233600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>192100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>194500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>248100</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>232700</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>187500</v>
+      </c>
+      <c r="E46" s="3">
         <v>197100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>191400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>211800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>217900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>218900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>226500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>213500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>229100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>210700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>220700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>211700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>285700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>308400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>329200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>351200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>357100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>370200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>136700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>72500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>68400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>84200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>103100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>106800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>138900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>138200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>135300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>138000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>175300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>170100</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI46" s="3">
+      <c r="AI46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ46" s="3">
         <v>519200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>543200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>507500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>612500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>633100</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>652100</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4774,8 +4879,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>10000</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>10000</v>
@@ -4786,8 +4891,8 @@
       <c r="P47" s="3">
         <v>10000</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>8</v>
+      <c r="Q47" s="3">
+        <v>10000</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>8</v>
@@ -4804,8 +4909,8 @@
       <c r="V47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
@@ -4858,124 +4963,130 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>200500</v>
+      </c>
+      <c r="E48" s="3">
         <v>221400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>219300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>195700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>185200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>185900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>198400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>189100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>192800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>216500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>214800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>202700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>160600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>166300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>167100</v>
-      </c>
-      <c r="R48" s="3">
-        <v>167300</v>
       </c>
       <c r="S48" s="3">
         <v>167300</v>
       </c>
       <c r="T48" s="3">
+        <v>167300</v>
+      </c>
+      <c r="U48" s="3">
         <v>166200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>168700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>186900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>183200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>187500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>192300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>211400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>249000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>226100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>190800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>192500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>195900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>154700</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI48" s="3">
+      <c r="AI48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>537600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>486300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>491300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>547700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>568100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>603200</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5001,7 +5112,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L49" s="3">
         <v>1000</v>
@@ -5033,8 +5144,8 @@
       <c r="U49" s="3">
         <v>1000</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>8</v>
+      <c r="V49" s="3">
+        <v>1000</v>
       </c>
       <c r="W49" s="3" t="s">
         <v>8</v>
@@ -5051,8 +5162,8 @@
       <c r="AA49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB49" s="3">
-        <v>0</v>
+      <c r="AB49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC49" s="3">
         <v>0</v>
@@ -5066,32 +5177,35 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>8</v>
+      <c r="AG49" s="3">
+        <v>0</v>
       </c>
       <c r="AH49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AI49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>32200</v>
-      </c>
-      <c r="AJ49" s="3">
-        <v>31900</v>
       </c>
       <c r="AK49" s="3">
         <v>31900</v>
       </c>
       <c r="AL49" s="3">
+        <v>31900</v>
+      </c>
+      <c r="AM49" s="3">
         <v>35500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>35800</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>37200</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5320,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,124 +5439,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>46500</v>
+        <v>37500</v>
       </c>
       <c r="E52" s="3">
+        <v>28300</v>
+      </c>
+      <c r="F52" s="3">
         <v>19600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>44400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>36600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>55300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>37100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>51800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>54700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>53500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>47200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>41800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>42900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>34200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>31900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>36400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>33800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>29700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>30400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>29700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>26500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>25300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>24600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>14500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>18400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>53400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>51700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>44900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>18500</v>
       </c>
-      <c r="AF52" s="3">
-        <v>0</v>
-      </c>
       <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
         <v>11000</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI52" s="3">
+      <c r="AI52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>66000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>65000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>57800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>50800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>51700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>46400</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5677,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>442900</v>
+      </c>
+      <c r="E54" s="3">
         <v>464900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>447600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>470100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>457800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>463500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>478400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>454400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>477700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>481700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>493900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>467200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>500300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>519900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>529300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>556000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>559200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>567100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>336900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>289100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>278000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>296900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>319900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>332700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>406300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>417700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>377700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>375400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>389600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>335700</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI54" s="3">
+      <c r="AI54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ54" s="3">
         <v>1154900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1126300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1088400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1246600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1288700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1338900</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5841,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,588 +5884,604 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E57" s="3">
         <v>14400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>24300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>21200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>20400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>14000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>10800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>24600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>23700</v>
       </c>
-      <c r="AF57" s="3">
-        <v>0</v>
-      </c>
       <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="3">
         <v>25800</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI57" s="3">
+      <c r="AI57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>203200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>221600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>223300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>281300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>280600</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>302000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E58" s="3">
         <v>7300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>12200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>11400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>12300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>12800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>23000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>49100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>43500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>42100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>43900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>47800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>57100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>108900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>101900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>44500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>7100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>15100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>23700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>6600</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI58" s="3">
+      <c r="AI58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>671400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>647600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>595400</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>699000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>716500</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>735600</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>25100</v>
+        <v>25500</v>
       </c>
       <c r="E59" s="3">
+        <v>24800</v>
+      </c>
+      <c r="F59" s="3">
         <v>25200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>25700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>25400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>26400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>28500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>26600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>25700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>23900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>25200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>20000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>19300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>19600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>23500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>32900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>19900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>27000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>38600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>41100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>42400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>43100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>56500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>77200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>61600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>73500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>112800</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>150800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>101600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>85700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>82600</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>89900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>91500</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E60" s="3">
         <v>48900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>49500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>48800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>51000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>57700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>57000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>39500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>41800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>43700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>43300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>34000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>31100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>33800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>35100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>36400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>36500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>51100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>88300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>73200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>75900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>89400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>109400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>113500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>162800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>170900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>133700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>93300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>104700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>145200</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI60" s="3">
+      <c r="AI60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ60" s="3">
         <v>1025400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>970800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>904400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1062900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1087000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>1129100</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>74400</v>
+      </c>
+      <c r="E61" s="3">
         <v>70700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>56500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>58200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>55700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>53600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>54500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>51000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>53500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>57900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>37500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>38000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>21200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>26900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>30000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>31700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>36100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>38800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>44000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>48100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>44800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>52500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>50100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>68400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>81200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>89100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>119300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>153200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>157800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>32500</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
       <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>30300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>31100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>28800</v>
       </c>
-      <c r="AL61" s="3">
-        <v>0</v>
-      </c>
       <c r="AM61" s="3">
         <v>0</v>
       </c>
       <c r="AN61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO61" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6366,92 +6512,95 @@
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="3">
         <v>24400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>15500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>15800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>19500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>19700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>20100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>21400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>20400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>21200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>22600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>22900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>21500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>33600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>35300</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE62" s="3">
-        <v>0</v>
+      <c r="AE62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF62" s="3">
         <v>0</v>
       </c>
       <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3">
         <v>67500</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI62" s="3">
+      <c r="AI62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>84400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>82600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>89000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>92000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>89500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>93600</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6715,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6834,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +6953,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>122600</v>
+      </c>
+      <c r="E66" s="3">
         <v>123300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>109500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>110700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>110200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>114800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>115000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>93800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>98900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>105100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>146600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>128100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>110100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>120400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>125300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>133000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>137200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>153800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>197800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>185700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>184400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>206600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>225200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>238300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>313900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>329600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>287000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>280700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>294400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>245200</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI66" s="3">
+      <c r="AI66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>1141000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1084400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1022300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1154900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1176400</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1224200</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7117,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7234,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7353,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7472,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7591,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-450000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-451500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-453000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-441300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-446100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-446500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-440600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-438600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-429200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-437600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-437400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-431600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-434600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-434400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-432700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-431100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-431800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-438800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-439600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-441500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-443700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-446700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-442300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-431400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-433800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-438900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-433500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-428400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-429900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-435500</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>-524700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-493200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-470000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-444500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-424000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-429500</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7829,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7948,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8067,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>310500</v>
+      </c>
+      <c r="E76" s="3">
         <v>304100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>300500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>319600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>309700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>311000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>325300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>322300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>340500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>335700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>347300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>339100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>390200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>399500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>404000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>422900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>422000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>413300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>139100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>103300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>93600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>90300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>94700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>94400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>92400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>88100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>90700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>94800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>95200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>90500</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI76" s="3">
+      <c r="AI76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>13900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>41900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>66100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>91700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>112300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>114700</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,129 +8305,135 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42551</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42460</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8246,115 +8441,118 @@
         <v>1500</v>
       </c>
       <c r="E81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-11800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>7000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-10900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>5400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3200</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI81" s="3">
+      <c r="AI81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>-31500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-23200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-25500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-20500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>5500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,43 +8593,44 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E83" s="3">
         <v>1800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2000</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M83" s="3">
         <v>1500</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
@@ -8484,35 +8683,38 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH83" s="3">
         <v>4500</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI83" s="3">
+      <c r="AI83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>17800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>20900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>24100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>19900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>18100</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8829,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8948,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9067,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9186,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,77 +9305,80 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>7200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-23700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-10600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-14400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>8800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-5100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-10500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>5300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>8</v>
       </c>
@@ -9177,38 +9394,41 @@
       <c r="AD89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH89" s="3">
         <v>18400</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI89" s="3">
+      <c r="AI89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-33800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>44600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-3500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-9100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,41 +9469,42 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2000</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -9338,35 +9559,38 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-80300</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-11300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-11400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9705,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,77 +9824,80 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>6900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>10100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-31200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>26100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>1200</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>8</v>
       </c>
@@ -9683,38 +9913,41 @@
       <c r="AD94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-156400</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI94" s="3">
+      <c r="AI94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-30100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>17900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>26000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>5200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,8 +9988,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9787,8 +10021,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9871,8 +10105,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10224,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10343,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,77 +10462,80 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E100" s="3">
         <v>13200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-16200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>4600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-45700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-23700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-14300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>244800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>32600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>8300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-9400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>8</v>
       </c>
@@ -10305,107 +10551,110 @@
       <c r="AD100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH100" s="3">
         <v>102400</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI100" s="3">
+      <c r="AI100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>16000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>50700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-48900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-4200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
         <v>2500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-5200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1900</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z101" s="3" t="s">
         <v>8</v>
       </c>
@@ -10421,107 +10670,110 @@
       <c r="AD101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH101" s="3">
         <v>11600</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI101" s="3">
+      <c r="AI101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>2500</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>2400</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-6800</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E102" s="3">
         <v>3600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>14300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-15100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-15100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>11000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-40600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-15700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-85000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-14900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-31500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-21500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-15000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>260300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>24300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>4300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-8100</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>8</v>
       </c>
@@ -10537,34 +10789,37 @@
       <c r="AD102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-23900</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI102" s="3">
+      <c r="AI102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-10700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>8500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>5100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-15000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>600</v>
       </c>
     </row>
